--- a/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E29B4975-C7DE-49C6-958D-B425045A536C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB6F26B9-7F53-443C-9584-CC8C1B73BA05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6748,7 +6748,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3336A893-7F76-4CF0-A075-0A3E428E7ED9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D197F9CE-BC27-45CB-BA21-0DE2B58000DB}">
   <dimension ref="B2:AE1032"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB6F26B9-7F53-443C-9584-CC8C1B73BA05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5D43B21-8F58-48FA-A99D-7911339B5E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6748,7 +6748,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D197F9CE-BC27-45CB-BA21-0DE2B58000DB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AFA9278-9043-4FB7-9FC8-771F57781D9D}">
   <dimension ref="B2:AE1032"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5D43B21-8F58-48FA-A99D-7911339B5E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{482CA4B4-954A-4D55-BA8F-1D5D0B174D60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6748,7 +6748,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AFA9278-9043-4FB7-9FC8-771F57781D9D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F06D137-8DD8-4101-9098-F482BBE4D8AC}">
   <dimension ref="B2:AE1032"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{735DC4BE-BB00-46CD-ABAE-D78A3D977627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B88404CD-C631-4A1E-895B-9FC9AB351ED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6426,7 +6426,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38BC588E-7E3E-4C48-B974-721E600D6D98}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1DB3778-F9D3-48D7-A531-4F4E760635EE}">
   <dimension ref="B2:AE915"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B88404CD-C631-4A1E-895B-9FC9AB351ED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9BFBAAF-B642-436C-9F55-E7E0ED8A66BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="12682" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="5" r:id="rId1"/>
@@ -6426,7 +6426,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1DB3778-F9D3-48D7-A531-4F4E760635EE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A59B710-70CD-4D8A-BE0A-85181BCE3D06}">
   <dimension ref="B2:AE915"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9BFBAAF-B642-436C-9F55-E7E0ED8A66BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B207D1A-F1B3-4CA3-A681-CA9DF6EAEA19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="12682" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="12683" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="5" r:id="rId1"/>
@@ -6426,7 +6426,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A59B710-70CD-4D8A-BE0A-85181BCE3D06}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0315B8E-7B0B-4492-A1A6-43CCC5700BCB}">
   <dimension ref="B2:AE915"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B207D1A-F1B3-4CA3-A681-CA9DF6EAEA19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7CD00E1E-693A-4AFE-8ABA-4CBE80763281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="12683" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="5" r:id="rId1"/>
@@ -6426,7 +6426,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0315B8E-7B0B-4492-A1A6-43CCC5700BCB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D91C6E8F-BFE1-4014-8B4A-4FFF5489E0D9}">
   <dimension ref="B2:AE915"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7CD00E1E-693A-4AFE-8ABA-4CBE80763281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3DA0A47C-4E40-4ACB-B8C9-4329B9D3A481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6426,7 +6426,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D91C6E8F-BFE1-4014-8B4A-4FFF5489E0D9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C6288E6-4B8F-490E-AD6E-2D7744AB68E3}">
   <dimension ref="B2:AE915"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3DA0A47C-4E40-4ACB-B8C9-4329B9D3A481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A89DDD7-8F2A-41BC-848C-745AC5831F46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -124,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8212" uniqueCount="1939">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8212" uniqueCount="2073">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -4659,334 +4659,736 @@
     <t>Steam Coal - ULTRASUPERCRITICAL_w526061686-525</t>
   </si>
   <si>
-    <t>EN_Hydro_w302931307-440</t>
+    <t>EN_Hydro_BRA-1_w302931307-440</t>
   </si>
   <si>
     <t>e_w302931307-440</t>
   </si>
   <si>
-    <t>EN_Hydro_BR587-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_BR525-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_BR293-500</t>
+    <t>EN_Hydro_BRA-2_w302931307-440</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_w302931307-440</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR587-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-2_BR587-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR587-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR525-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-2_BR525-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR525-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR293-500</t>
   </si>
   <si>
     <t>e_BR293-500</t>
   </si>
   <si>
-    <t>EN_Hydro_BR535-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_BR820-500</t>
+    <t>EN_Hydro_BRA-2_BR293-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR293-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR535-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-2_BR535-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR535-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR820-500</t>
   </si>
   <si>
     <t>e_BR820-500</t>
   </si>
   <si>
-    <t>EN_Hydro_w304646981-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_BR646-440</t>
+    <t>EN_Hydro_BRA-2_BR820-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR820-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_w304646981-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-2_w304646981-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_w304646981-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR646-440</t>
   </si>
   <si>
     <t>e_BR646-440</t>
   </si>
   <si>
-    <t>EN_Hydro_BR661-440</t>
+    <t>EN_Hydro_BRA-2_BR646-440</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR646-440</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR661-440</t>
   </si>
   <si>
     <t>e_BR661-440</t>
   </si>
   <si>
-    <t>EN_Hydro_BR866-500</t>
+    <t>EN_Hydro_BRA-2_BR661-440</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR661-440</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR866-500</t>
   </si>
   <si>
     <t>e_BR866-500</t>
   </si>
   <si>
-    <t>EN_Hydro_BR52-500</t>
+    <t>EN_Hydro_BRA-2_BR866-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR866-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR52-500</t>
   </si>
   <si>
     <t>e_BR52-500</t>
   </si>
   <si>
-    <t>EN_Hydro_BR185-500</t>
+    <t>EN_Hydro_BRA-2_BR52-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR52-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR185-500</t>
   </si>
   <si>
     <t>e_BR185-500</t>
   </si>
   <si>
-    <t>EN_Hydro_w525253078-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_r6844204-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_w140181432-500</t>
+    <t>EN_Hydro_BRA-2_BR185-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR185-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_w525253078-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-2_w525253078-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_w525253078-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_r6844204-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-2_r6844204-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_r6844204-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_w140181432-500</t>
   </si>
   <si>
     <t>e_w140181432-500</t>
   </si>
   <si>
-    <t>EN_Hydro_BR433-500</t>
+    <t>EN_Hydro_BRA-2_w140181432-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_w140181432-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR433-500</t>
   </si>
   <si>
     <t>e_BR433-500</t>
   </si>
   <si>
-    <t>EN_Hydro_BR676-440</t>
-  </si>
-  <si>
-    <t>EN_Hydro_BR347-500</t>
+    <t>EN_Hydro_BRA-2_BR433-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR433-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR676-440</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-2_BR676-440</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR676-440</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR347-500</t>
   </si>
   <si>
     <t>e_BR347-500</t>
   </si>
   <si>
-    <t>EN_Hydro_w307168542-230</t>
+    <t>EN_Hydro_BRA-2_BR347-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR347-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_w307168542-230</t>
   </si>
   <si>
     <t>e_w307168542-230</t>
   </si>
   <si>
-    <t>EN_Hydro_BR602-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_BR184-500</t>
+    <t>EN_Hydro_BRA-2_w307168542-230</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_w307168542-230</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR602-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-2_BR602-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR602-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR184-500</t>
   </si>
   <si>
     <t>e_BR184-500</t>
   </si>
   <si>
-    <t>EN_Hydro_w626479359-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_w188465343-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_BR596-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_BR659-500</t>
+    <t>EN_Hydro_BRA-2_BR184-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR184-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_w626479359-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-2_w626479359-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_w626479359-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_w188465343-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-2_w188465343-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_w188465343-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR596-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-2_BR596-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR596-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR659-500</t>
   </si>
   <si>
     <t>e_BR659-500</t>
   </si>
   <si>
-    <t>EN_Hydro_BR838-500</t>
+    <t>EN_Hydro_BRA-2_BR659-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR659-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR838-500</t>
   </si>
   <si>
     <t>e_BR838-500</t>
   </si>
   <si>
-    <t>EN_Hydro_BR732-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_BR833-500</t>
+    <t>EN_Hydro_BRA-2_BR838-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR838-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR732-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-2_BR732-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR732-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR833-500</t>
   </si>
   <si>
     <t>e_BR833-500</t>
   </si>
   <si>
-    <t>EN_Hydro_BR786-500</t>
+    <t>EN_Hydro_BRA-2_BR833-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR833-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR786-500</t>
   </si>
   <si>
     <t>e_BR786-500</t>
   </si>
   <si>
-    <t>EN_Hydro_BR571-500</t>
+    <t>EN_Hydro_BRA-2_BR786-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR786-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR571-500</t>
   </si>
   <si>
     <t>e_BR571-500</t>
   </si>
   <si>
-    <t>EN_Hydro_BR758-440</t>
-  </si>
-  <si>
-    <t>EN_Hydro_BR592-500</t>
+    <t>EN_Hydro_BRA-2_BR571-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR571-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR758-440</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-2_BR758-440</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR758-440</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR592-500</t>
   </si>
   <si>
     <t>e_BR592-500</t>
   </si>
   <si>
-    <t>EN_Hydro_BR652-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_w286006777-440</t>
+    <t>EN_Hydro_BRA-2_BR592-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR592-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR652-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-2_BR652-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR652-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_w286006777-440</t>
   </si>
   <si>
     <t>e_w286006777-440</t>
   </si>
   <si>
-    <t>EN_Hydro_BR499-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_BR858-500</t>
+    <t>EN_Hydro_BRA-2_w286006777-440</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_w286006777-440</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR499-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-2_BR499-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR499-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR858-500</t>
   </si>
   <si>
     <t>e_BR858-500</t>
   </si>
   <si>
-    <t>EN_Hydro_BR803-500</t>
+    <t>EN_Hydro_BRA-2_BR858-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR858-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR803-500</t>
   </si>
   <si>
     <t>e_BR803-500</t>
   </si>
   <si>
-    <t>EN_Hydro_BR459-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_BR878-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_w168664395-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_BR285-500</t>
+    <t>EN_Hydro_BRA-2_BR803-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR803-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR459-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-2_BR459-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR459-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR878-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-2_BR878-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR878-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_w168664395-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-2_w168664395-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_w168664395-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR285-500</t>
   </si>
   <si>
     <t>e_BR285-500</t>
   </si>
   <si>
-    <t>EN_Hydro_w302901044-440</t>
-  </si>
-  <si>
-    <t>EN_Hydro_BR310-500</t>
+    <t>EN_Hydro_BRA-2_BR285-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR285-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_w302901044-440</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-2_w302901044-440</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_w302901044-440</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR310-500</t>
   </si>
   <si>
     <t>e_BR310-500</t>
   </si>
   <si>
-    <t>EN_Hydro_BR282-500</t>
+    <t>EN_Hydro_BRA-2_BR310-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR310-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR282-500</t>
   </si>
   <si>
     <t>e_BR282-500</t>
   </si>
   <si>
-    <t>EN_Hydro_w521542011-500</t>
+    <t>EN_Hydro_BRA-2_BR282-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR282-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_w521542011-500</t>
   </si>
   <si>
     <t>e_w521542011-500</t>
   </si>
   <si>
-    <t>EN_Hydro_BR606-500</t>
+    <t>EN_Hydro_BRA-2_w521542011-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_w521542011-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR606-500</t>
   </si>
   <si>
     <t>e_BR606-500</t>
   </si>
   <si>
-    <t>EN_Hydro_BR579-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_BR550-500</t>
+    <t>EN_Hydro_BRA-2_BR606-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR606-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR579-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-2_BR579-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR579-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR550-500</t>
   </si>
   <si>
     <t>e_BR550-500</t>
   </si>
   <si>
-    <t>EN_Hydro_BR632-440</t>
+    <t>EN_Hydro_BRA-2_BR550-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR550-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR632-440</t>
   </si>
   <si>
     <t>e_BR632-440</t>
   </si>
   <si>
-    <t>EN_Hydro_BR412-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_BR384-500</t>
+    <t>EN_Hydro_BRA-2_BR632-440</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR632-440</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR412-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-2_BR412-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR412-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR384-500</t>
   </si>
   <si>
     <t>e_BR384-500</t>
   </si>
   <si>
-    <t>EN_Hydro_BR657-440</t>
-  </si>
-  <si>
-    <t>EN_Hydro_w150728360-500</t>
+    <t>EN_Hydro_BRA-2_BR384-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR384-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR657-440</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-2_BR657-440</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR657-440</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_w150728360-500</t>
   </si>
   <si>
     <t>e_w150728360-500</t>
   </si>
   <si>
-    <t>EN_Hydro_w495013387-500</t>
+    <t>EN_Hydro_BRA-2_w150728360-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_w150728360-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_w495013387-500</t>
   </si>
   <si>
     <t>e_w495013387-500</t>
   </si>
   <si>
-    <t>EN_Hydro_BR270-230</t>
+    <t>EN_Hydro_BRA-2_w495013387-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_w495013387-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR270-230</t>
   </si>
   <si>
     <t>e_BR270-230</t>
   </si>
   <si>
-    <t>EN_Hydro_BR274-500</t>
-  </si>
-  <si>
-    <t>EN_Hydro_BR283-500</t>
+    <t>EN_Hydro_BRA-2_BR270-230</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR270-230</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR274-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-2_BR274-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR274-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR283-500</t>
   </si>
   <si>
     <t>e_BR283-500</t>
   </si>
   <si>
-    <t>EN_Hydro_BR543-500</t>
+    <t>EN_Hydro_BRA-2_BR283-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR283-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR543-500</t>
   </si>
   <si>
     <t>e_BR543-500</t>
   </si>
   <si>
-    <t>EN_Hydro_BR435-500</t>
+    <t>EN_Hydro_BRA-2_BR543-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR543-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR435-500</t>
   </si>
   <si>
     <t>e_BR435-500</t>
   </si>
   <si>
-    <t>EN_Hydro_BR353-500</t>
+    <t>EN_Hydro_BRA-2_BR435-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR435-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR353-500</t>
   </si>
   <si>
     <t>e_BR353-500</t>
   </si>
   <si>
-    <t>EN_Hydro_BR294-500</t>
+    <t>EN_Hydro_BRA-2_BR353-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR353-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR294-500</t>
   </si>
   <si>
     <t>e_BR294-500</t>
   </si>
   <si>
-    <t>EN_Hydro_BR662-440</t>
+    <t>EN_Hydro_BRA-2_BR294-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR294-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR662-440</t>
   </si>
   <si>
     <t>e_BR662-440</t>
   </si>
   <si>
-    <t>EN_Hydro_w453724535-500</t>
+    <t>EN_Hydro_BRA-2_BR662-440</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR662-440</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_w453724535-500</t>
   </si>
   <si>
     <t>e_w453724535-500</t>
   </si>
   <si>
-    <t>EN_Hydro_BR624-440</t>
+    <t>EN_Hydro_BRA-2_w453724535-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_w453724535-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR624-440</t>
   </si>
   <si>
     <t>e_BR624-440</t>
   </si>
   <si>
-    <t>EN_Hydro_BR506-500</t>
+    <t>EN_Hydro_BRA-2_BR624-440</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR624-440</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR506-500</t>
   </si>
   <si>
     <t>e_BR506-500</t>
   </si>
   <si>
-    <t>EN_Hydro_w215284729-500</t>
+    <t>EN_Hydro_BRA-2_BR506-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR506-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_w215284729-500</t>
   </si>
   <si>
     <t>e_w215284729-500</t>
   </si>
   <si>
-    <t>EN_Hydro_BR302-500</t>
+    <t>EN_Hydro_BRA-2_w215284729-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_w215284729-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-1_BR302-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-2_BR302-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_BRA-3_BR302-500</t>
   </si>
   <si>
     <t>EN_STG8hbNREL_w287393618-500</t>
@@ -6426,7 +6828,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C6288E6-4B8F-490E-AD6E-2D7744AB68E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C51C672-03AE-4463-8578-94F4EF7EA31C}">
   <dimension ref="B2:AE915"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6550,16 +6952,16 @@
         <v>581</v>
       </c>
       <c r="AB4" t="s">
-        <v>1933</v>
+        <v>2067</v>
       </c>
       <c r="AC4" t="s">
-        <v>1935</v>
+        <v>2069</v>
       </c>
       <c r="AD4" t="s">
-        <v>1936</v>
+        <v>2070</v>
       </c>
       <c r="AE4" t="s">
-        <v>1937</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="5" spans="2:31" x14ac:dyDescent="0.45">
@@ -6612,10 +7014,10 @@
         <v>1067</v>
       </c>
       <c r="AA5" t="s">
-        <v>1932</v>
+        <v>2066</v>
       </c>
       <c r="AB5" t="s">
-        <v>1934</v>
+        <v>2068</v>
       </c>
       <c r="AC5">
         <v>2</v>
@@ -6624,7 +7026,7 @@
         <v>0</v>
       </c>
       <c r="AE5" t="s">
-        <v>1938</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="6" spans="2:31" x14ac:dyDescent="0.45">
@@ -26844,7 +27246,7 @@
         <v>91</v>
       </c>
       <c r="V434" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="W434" t="s">
         <v>1512</v>
@@ -26870,7 +27272,7 @@
         <v>91</v>
       </c>
       <c r="V435" t="s">
-        <v>1511</v>
+        <v>1514</v>
       </c>
       <c r="W435" t="s">
         <v>1512</v>
@@ -26896,7 +27298,7 @@
         <v>91</v>
       </c>
       <c r="V436" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="W436" t="s">
         <v>1036</v>
@@ -26922,7 +27324,7 @@
         <v>91</v>
       </c>
       <c r="V437" t="s">
-        <v>1513</v>
+        <v>1516</v>
       </c>
       <c r="W437" t="s">
         <v>1036</v>
@@ -26948,7 +27350,7 @@
         <v>91</v>
       </c>
       <c r="V438" t="s">
-        <v>1513</v>
+        <v>1517</v>
       </c>
       <c r="W438" t="s">
         <v>1036</v>
@@ -26974,7 +27376,7 @@
         <v>91</v>
       </c>
       <c r="V439" t="s">
-        <v>1514</v>
+        <v>1518</v>
       </c>
       <c r="W439" t="s">
         <v>1002</v>
@@ -27000,7 +27402,7 @@
         <v>91</v>
       </c>
       <c r="V440" t="s">
-        <v>1514</v>
+        <v>1519</v>
       </c>
       <c r="W440" t="s">
         <v>1002</v>
@@ -27026,7 +27428,7 @@
         <v>91</v>
       </c>
       <c r="V441" t="s">
-        <v>1514</v>
+        <v>1520</v>
       </c>
       <c r="W441" t="s">
         <v>1002</v>
@@ -27052,10 +27454,10 @@
         <v>91</v>
       </c>
       <c r="V442" t="s">
-        <v>1515</v>
+        <v>1521</v>
       </c>
       <c r="W442" t="s">
-        <v>1516</v>
+        <v>1522</v>
       </c>
       <c r="X442" t="s">
         <v>1067</v>
@@ -27078,10 +27480,10 @@
         <v>91</v>
       </c>
       <c r="V443" t="s">
-        <v>1515</v>
+        <v>1523</v>
       </c>
       <c r="W443" t="s">
-        <v>1516</v>
+        <v>1522</v>
       </c>
       <c r="X443" t="s">
         <v>1067</v>
@@ -27104,10 +27506,10 @@
         <v>91</v>
       </c>
       <c r="V444" t="s">
-        <v>1515</v>
+        <v>1524</v>
       </c>
       <c r="W444" t="s">
-        <v>1516</v>
+        <v>1522</v>
       </c>
       <c r="X444" t="s">
         <v>1067</v>
@@ -27130,7 +27532,7 @@
         <v>91</v>
       </c>
       <c r="V445" t="s">
-        <v>1517</v>
+        <v>1525</v>
       </c>
       <c r="W445" t="s">
         <v>1034</v>
@@ -27156,7 +27558,7 @@
         <v>91</v>
       </c>
       <c r="V446" t="s">
-        <v>1517</v>
+        <v>1526</v>
       </c>
       <c r="W446" t="s">
         <v>1034</v>
@@ -27182,7 +27584,7 @@
         <v>91</v>
       </c>
       <c r="V447" t="s">
-        <v>1517</v>
+        <v>1527</v>
       </c>
       <c r="W447" t="s">
         <v>1034</v>
@@ -27208,10 +27610,10 @@
         <v>91</v>
       </c>
       <c r="V448" t="s">
-        <v>1518</v>
+        <v>1528</v>
       </c>
       <c r="W448" t="s">
-        <v>1519</v>
+        <v>1529</v>
       </c>
       <c r="X448" t="s">
         <v>1067</v>
@@ -27234,10 +27636,10 @@
         <v>91</v>
       </c>
       <c r="V449" t="s">
-        <v>1518</v>
+        <v>1530</v>
       </c>
       <c r="W449" t="s">
-        <v>1519</v>
+        <v>1529</v>
       </c>
       <c r="X449" t="s">
         <v>1067</v>
@@ -27260,10 +27662,10 @@
         <v>91</v>
       </c>
       <c r="V450" t="s">
-        <v>1518</v>
+        <v>1531</v>
       </c>
       <c r="W450" t="s">
-        <v>1519</v>
+        <v>1529</v>
       </c>
       <c r="X450" t="s">
         <v>1067</v>
@@ -27286,7 +27688,7 @@
         <v>91</v>
       </c>
       <c r="V451" t="s">
-        <v>1520</v>
+        <v>1532</v>
       </c>
       <c r="W451" t="s">
         <v>1175</v>
@@ -27312,7 +27714,7 @@
         <v>91</v>
       </c>
       <c r="V452" t="s">
-        <v>1520</v>
+        <v>1533</v>
       </c>
       <c r="W452" t="s">
         <v>1175</v>
@@ -27338,7 +27740,7 @@
         <v>91</v>
       </c>
       <c r="V453" t="s">
-        <v>1520</v>
+        <v>1534</v>
       </c>
       <c r="W453" t="s">
         <v>1175</v>
@@ -27364,10 +27766,10 @@
         <v>91</v>
       </c>
       <c r="V454" t="s">
-        <v>1521</v>
+        <v>1535</v>
       </c>
       <c r="W454" t="s">
-        <v>1522</v>
+        <v>1536</v>
       </c>
       <c r="X454" t="s">
         <v>1067</v>
@@ -27390,10 +27792,10 @@
         <v>91</v>
       </c>
       <c r="V455" t="s">
-        <v>1521</v>
+        <v>1537</v>
       </c>
       <c r="W455" t="s">
-        <v>1522</v>
+        <v>1536</v>
       </c>
       <c r="X455" t="s">
         <v>1067</v>
@@ -27416,10 +27818,10 @@
         <v>91</v>
       </c>
       <c r="V456" t="s">
-        <v>1521</v>
+        <v>1538</v>
       </c>
       <c r="W456" t="s">
-        <v>1522</v>
+        <v>1536</v>
       </c>
       <c r="X456" t="s">
         <v>1067</v>
@@ -27442,10 +27844,10 @@
         <v>91</v>
       </c>
       <c r="V457" t="s">
-        <v>1523</v>
+        <v>1539</v>
       </c>
       <c r="W457" t="s">
-        <v>1524</v>
+        <v>1540</v>
       </c>
       <c r="X457" t="s">
         <v>1067</v>
@@ -27468,10 +27870,10 @@
         <v>91</v>
       </c>
       <c r="V458" t="s">
-        <v>1523</v>
+        <v>1541</v>
       </c>
       <c r="W458" t="s">
-        <v>1524</v>
+        <v>1540</v>
       </c>
       <c r="X458" t="s">
         <v>1067</v>
@@ -27494,10 +27896,10 @@
         <v>91</v>
       </c>
       <c r="V459" t="s">
-        <v>1523</v>
+        <v>1542</v>
       </c>
       <c r="W459" t="s">
-        <v>1524</v>
+        <v>1540</v>
       </c>
       <c r="X459" t="s">
         <v>1067</v>
@@ -27520,10 +27922,10 @@
         <v>91</v>
       </c>
       <c r="V460" t="s">
-        <v>1525</v>
+        <v>1543</v>
       </c>
       <c r="W460" t="s">
-        <v>1526</v>
+        <v>1544</v>
       </c>
       <c r="X460" t="s">
         <v>1067</v>
@@ -27546,10 +27948,10 @@
         <v>91</v>
       </c>
       <c r="V461" t="s">
-        <v>1525</v>
+        <v>1545</v>
       </c>
       <c r="W461" t="s">
-        <v>1526</v>
+        <v>1544</v>
       </c>
       <c r="X461" t="s">
         <v>1067</v>
@@ -27572,10 +27974,10 @@
         <v>91</v>
       </c>
       <c r="V462" t="s">
-        <v>1525</v>
+        <v>1546</v>
       </c>
       <c r="W462" t="s">
-        <v>1526</v>
+        <v>1544</v>
       </c>
       <c r="X462" t="s">
         <v>1067</v>
@@ -27598,10 +28000,10 @@
         <v>91</v>
       </c>
       <c r="V463" t="s">
-        <v>1527</v>
+        <v>1547</v>
       </c>
       <c r="W463" t="s">
-        <v>1528</v>
+        <v>1548</v>
       </c>
       <c r="X463" t="s">
         <v>1067</v>
@@ -27624,10 +28026,10 @@
         <v>91</v>
       </c>
       <c r="V464" t="s">
-        <v>1527</v>
+        <v>1549</v>
       </c>
       <c r="W464" t="s">
-        <v>1528</v>
+        <v>1548</v>
       </c>
       <c r="X464" t="s">
         <v>1067</v>
@@ -27650,10 +28052,10 @@
         <v>91</v>
       </c>
       <c r="V465" t="s">
-        <v>1527</v>
+        <v>1550</v>
       </c>
       <c r="W465" t="s">
-        <v>1528</v>
+        <v>1548</v>
       </c>
       <c r="X465" t="s">
         <v>1067</v>
@@ -27676,10 +28078,10 @@
         <v>91</v>
       </c>
       <c r="V466" t="s">
-        <v>1529</v>
+        <v>1551</v>
       </c>
       <c r="W466" t="s">
-        <v>1530</v>
+        <v>1552</v>
       </c>
       <c r="X466" t="s">
         <v>1067</v>
@@ -27702,10 +28104,10 @@
         <v>91</v>
       </c>
       <c r="V467" t="s">
-        <v>1529</v>
+        <v>1553</v>
       </c>
       <c r="W467" t="s">
-        <v>1530</v>
+        <v>1552</v>
       </c>
       <c r="X467" t="s">
         <v>1067</v>
@@ -27728,10 +28130,10 @@
         <v>91</v>
       </c>
       <c r="V468" t="s">
-        <v>1529</v>
+        <v>1554</v>
       </c>
       <c r="W468" t="s">
-        <v>1530</v>
+        <v>1552</v>
       </c>
       <c r="X468" t="s">
         <v>1067</v>
@@ -27754,7 +28156,7 @@
         <v>91</v>
       </c>
       <c r="V469" t="s">
-        <v>1531</v>
+        <v>1555</v>
       </c>
       <c r="W469" t="s">
         <v>979</v>
@@ -27780,7 +28182,7 @@
         <v>91</v>
       </c>
       <c r="V470" t="s">
-        <v>1531</v>
+        <v>1556</v>
       </c>
       <c r="W470" t="s">
         <v>979</v>
@@ -27806,7 +28208,7 @@
         <v>91</v>
       </c>
       <c r="V471" t="s">
-        <v>1531</v>
+        <v>1557</v>
       </c>
       <c r="W471" t="s">
         <v>979</v>
@@ -27832,7 +28234,7 @@
         <v>91</v>
       </c>
       <c r="V472" t="s">
-        <v>1532</v>
+        <v>1558</v>
       </c>
       <c r="W472" t="s">
         <v>985</v>
@@ -27858,7 +28260,7 @@
         <v>91</v>
       </c>
       <c r="V473" t="s">
-        <v>1532</v>
+        <v>1559</v>
       </c>
       <c r="W473" t="s">
         <v>985</v>
@@ -27884,7 +28286,7 @@
         <v>91</v>
       </c>
       <c r="V474" t="s">
-        <v>1532</v>
+        <v>1560</v>
       </c>
       <c r="W474" t="s">
         <v>985</v>
@@ -27910,10 +28312,10 @@
         <v>91</v>
       </c>
       <c r="V475" t="s">
-        <v>1533</v>
+        <v>1561</v>
       </c>
       <c r="W475" t="s">
-        <v>1534</v>
+        <v>1562</v>
       </c>
       <c r="X475" t="s">
         <v>1067</v>
@@ -27936,10 +28338,10 @@
         <v>91</v>
       </c>
       <c r="V476" t="s">
-        <v>1533</v>
+        <v>1563</v>
       </c>
       <c r="W476" t="s">
-        <v>1534</v>
+        <v>1562</v>
       </c>
       <c r="X476" t="s">
         <v>1067</v>
@@ -27962,10 +28364,10 @@
         <v>91</v>
       </c>
       <c r="V477" t="s">
-        <v>1533</v>
+        <v>1564</v>
       </c>
       <c r="W477" t="s">
-        <v>1534</v>
+        <v>1562</v>
       </c>
       <c r="X477" t="s">
         <v>1067</v>
@@ -27988,10 +28390,10 @@
         <v>91</v>
       </c>
       <c r="V478" t="s">
-        <v>1535</v>
+        <v>1565</v>
       </c>
       <c r="W478" t="s">
-        <v>1536</v>
+        <v>1566</v>
       </c>
       <c r="X478" t="s">
         <v>1067</v>
@@ -28014,10 +28416,10 @@
         <v>91</v>
       </c>
       <c r="V479" t="s">
-        <v>1535</v>
+        <v>1567</v>
       </c>
       <c r="W479" t="s">
-        <v>1536</v>
+        <v>1566</v>
       </c>
       <c r="X479" t="s">
         <v>1067</v>
@@ -28040,10 +28442,10 @@
         <v>91</v>
       </c>
       <c r="V480" t="s">
-        <v>1535</v>
+        <v>1568</v>
       </c>
       <c r="W480" t="s">
-        <v>1536</v>
+        <v>1566</v>
       </c>
       <c r="X480" t="s">
         <v>1067</v>
@@ -28066,7 +28468,7 @@
         <v>91</v>
       </c>
       <c r="V481" t="s">
-        <v>1537</v>
+        <v>1569</v>
       </c>
       <c r="W481" t="s">
         <v>988</v>
@@ -28092,7 +28494,7 @@
         <v>91</v>
       </c>
       <c r="V482" t="s">
-        <v>1537</v>
+        <v>1570</v>
       </c>
       <c r="W482" t="s">
         <v>988</v>
@@ -28118,7 +28520,7 @@
         <v>91</v>
       </c>
       <c r="V483" t="s">
-        <v>1537</v>
+        <v>1571</v>
       </c>
       <c r="W483" t="s">
         <v>988</v>
@@ -28144,10 +28546,10 @@
         <v>91</v>
       </c>
       <c r="V484" t="s">
-        <v>1538</v>
+        <v>1572</v>
       </c>
       <c r="W484" t="s">
-        <v>1539</v>
+        <v>1573</v>
       </c>
       <c r="X484" t="s">
         <v>1067</v>
@@ -28170,10 +28572,10 @@
         <v>91</v>
       </c>
       <c r="V485" t="s">
-        <v>1538</v>
+        <v>1574</v>
       </c>
       <c r="W485" t="s">
-        <v>1539</v>
+        <v>1573</v>
       </c>
       <c r="X485" t="s">
         <v>1067</v>
@@ -28196,10 +28598,10 @@
         <v>91</v>
       </c>
       <c r="V486" t="s">
-        <v>1538</v>
+        <v>1575</v>
       </c>
       <c r="W486" t="s">
-        <v>1539</v>
+        <v>1573</v>
       </c>
       <c r="X486" t="s">
         <v>1067</v>
@@ -28222,10 +28624,10 @@
         <v>91</v>
       </c>
       <c r="V487" t="s">
-        <v>1540</v>
+        <v>1576</v>
       </c>
       <c r="W487" t="s">
-        <v>1541</v>
+        <v>1577</v>
       </c>
       <c r="X487" t="s">
         <v>1067</v>
@@ -28248,10 +28650,10 @@
         <v>91</v>
       </c>
       <c r="V488" t="s">
-        <v>1540</v>
+        <v>1578</v>
       </c>
       <c r="W488" t="s">
-        <v>1541</v>
+        <v>1577</v>
       </c>
       <c r="X488" t="s">
         <v>1067</v>
@@ -28262,10 +28664,10 @@
         <v>91</v>
       </c>
       <c r="V489" t="s">
-        <v>1540</v>
+        <v>1579</v>
       </c>
       <c r="W489" t="s">
-        <v>1541</v>
+        <v>1577</v>
       </c>
       <c r="X489" t="s">
         <v>1067</v>
@@ -28276,7 +28678,7 @@
         <v>91</v>
       </c>
       <c r="V490" t="s">
-        <v>1542</v>
+        <v>1580</v>
       </c>
       <c r="W490" t="s">
         <v>1027</v>
@@ -28290,7 +28692,7 @@
         <v>91</v>
       </c>
       <c r="V491" t="s">
-        <v>1542</v>
+        <v>1581</v>
       </c>
       <c r="W491" t="s">
         <v>1027</v>
@@ -28304,7 +28706,7 @@
         <v>91</v>
       </c>
       <c r="V492" t="s">
-        <v>1542</v>
+        <v>1582</v>
       </c>
       <c r="W492" t="s">
         <v>1027</v>
@@ -28318,10 +28720,10 @@
         <v>91</v>
       </c>
       <c r="V493" t="s">
-        <v>1543</v>
+        <v>1583</v>
       </c>
       <c r="W493" t="s">
-        <v>1544</v>
+        <v>1584</v>
       </c>
       <c r="X493" t="s">
         <v>1067</v>
@@ -28332,10 +28734,10 @@
         <v>91</v>
       </c>
       <c r="V494" t="s">
-        <v>1543</v>
+        <v>1585</v>
       </c>
       <c r="W494" t="s">
-        <v>1544</v>
+        <v>1584</v>
       </c>
       <c r="X494" t="s">
         <v>1067</v>
@@ -28346,10 +28748,10 @@
         <v>91</v>
       </c>
       <c r="V495" t="s">
-        <v>1543</v>
+        <v>1586</v>
       </c>
       <c r="W495" t="s">
-        <v>1544</v>
+        <v>1584</v>
       </c>
       <c r="X495" t="s">
         <v>1067</v>
@@ -28360,7 +28762,7 @@
         <v>91</v>
       </c>
       <c r="V496" t="s">
-        <v>1545</v>
+        <v>1587</v>
       </c>
       <c r="W496" t="s">
         <v>983</v>
@@ -28374,7 +28776,7 @@
         <v>91</v>
       </c>
       <c r="V497" t="s">
-        <v>1545</v>
+        <v>1588</v>
       </c>
       <c r="W497" t="s">
         <v>983</v>
@@ -28388,7 +28790,7 @@
         <v>91</v>
       </c>
       <c r="V498" t="s">
-        <v>1545</v>
+        <v>1589</v>
       </c>
       <c r="W498" t="s">
         <v>983</v>
@@ -28402,7 +28804,7 @@
         <v>91</v>
       </c>
       <c r="V499" t="s">
-        <v>1546</v>
+        <v>1590</v>
       </c>
       <c r="W499" t="s">
         <v>974</v>
@@ -28416,7 +28818,7 @@
         <v>91</v>
       </c>
       <c r="V500" t="s">
-        <v>1546</v>
+        <v>1591</v>
       </c>
       <c r="W500" t="s">
         <v>974</v>
@@ -28430,7 +28832,7 @@
         <v>91</v>
       </c>
       <c r="V501" t="s">
-        <v>1546</v>
+        <v>1592</v>
       </c>
       <c r="W501" t="s">
         <v>974</v>
@@ -28444,7 +28846,7 @@
         <v>91</v>
       </c>
       <c r="V502" t="s">
-        <v>1547</v>
+        <v>1593</v>
       </c>
       <c r="W502" t="s">
         <v>1004</v>
@@ -28458,7 +28860,7 @@
         <v>91</v>
       </c>
       <c r="V503" t="s">
-        <v>1547</v>
+        <v>1594</v>
       </c>
       <c r="W503" t="s">
         <v>1004</v>
@@ -28472,7 +28874,7 @@
         <v>91</v>
       </c>
       <c r="V504" t="s">
-        <v>1547</v>
+        <v>1595</v>
       </c>
       <c r="W504" t="s">
         <v>1004</v>
@@ -28486,10 +28888,10 @@
         <v>91</v>
       </c>
       <c r="V505" t="s">
-        <v>1548</v>
+        <v>1596</v>
       </c>
       <c r="W505" t="s">
-        <v>1549</v>
+        <v>1597</v>
       </c>
       <c r="X505" t="s">
         <v>1067</v>
@@ -28500,10 +28902,10 @@
         <v>91</v>
       </c>
       <c r="V506" t="s">
-        <v>1548</v>
+        <v>1598</v>
       </c>
       <c r="W506" t="s">
-        <v>1549</v>
+        <v>1597</v>
       </c>
       <c r="X506" t="s">
         <v>1067</v>
@@ -28514,10 +28916,10 @@
         <v>91</v>
       </c>
       <c r="V507" t="s">
-        <v>1548</v>
+        <v>1599</v>
       </c>
       <c r="W507" t="s">
-        <v>1549</v>
+        <v>1597</v>
       </c>
       <c r="X507" t="s">
         <v>1067</v>
@@ -28528,10 +28930,10 @@
         <v>91</v>
       </c>
       <c r="V508" t="s">
-        <v>1550</v>
+        <v>1600</v>
       </c>
       <c r="W508" t="s">
-        <v>1551</v>
+        <v>1601</v>
       </c>
       <c r="X508" t="s">
         <v>1067</v>
@@ -28542,10 +28944,10 @@
         <v>91</v>
       </c>
       <c r="V509" t="s">
-        <v>1550</v>
+        <v>1602</v>
       </c>
       <c r="W509" t="s">
-        <v>1551</v>
+        <v>1601</v>
       </c>
       <c r="X509" t="s">
         <v>1067</v>
@@ -28556,10 +28958,10 @@
         <v>91</v>
       </c>
       <c r="V510" t="s">
-        <v>1550</v>
+        <v>1603</v>
       </c>
       <c r="W510" t="s">
-        <v>1551</v>
+        <v>1601</v>
       </c>
       <c r="X510" t="s">
         <v>1067</v>
@@ -28570,7 +28972,7 @@
         <v>91</v>
       </c>
       <c r="V511" t="s">
-        <v>1552</v>
+        <v>1604</v>
       </c>
       <c r="W511" t="s">
         <v>1021</v>
@@ -28584,7 +28986,7 @@
         <v>91</v>
       </c>
       <c r="V512" t="s">
-        <v>1552</v>
+        <v>1605</v>
       </c>
       <c r="W512" t="s">
         <v>1021</v>
@@ -28598,7 +29000,7 @@
         <v>91</v>
       </c>
       <c r="V513" t="s">
-        <v>1552</v>
+        <v>1606</v>
       </c>
       <c r="W513" t="s">
         <v>1021</v>
@@ -28612,10 +29014,10 @@
         <v>91</v>
       </c>
       <c r="V514" t="s">
-        <v>1553</v>
+        <v>1607</v>
       </c>
       <c r="W514" t="s">
-        <v>1554</v>
+        <v>1608</v>
       </c>
       <c r="X514" t="s">
         <v>1067</v>
@@ -28626,10 +29028,10 @@
         <v>91</v>
       </c>
       <c r="V515" t="s">
-        <v>1553</v>
+        <v>1609</v>
       </c>
       <c r="W515" t="s">
-        <v>1554</v>
+        <v>1608</v>
       </c>
       <c r="X515" t="s">
         <v>1067</v>
@@ -28640,10 +29042,10 @@
         <v>91</v>
       </c>
       <c r="V516" t="s">
-        <v>1553</v>
+        <v>1610</v>
       </c>
       <c r="W516" t="s">
-        <v>1554</v>
+        <v>1608</v>
       </c>
       <c r="X516" t="s">
         <v>1067</v>
@@ -28654,10 +29056,10 @@
         <v>91</v>
       </c>
       <c r="V517" t="s">
-        <v>1555</v>
+        <v>1611</v>
       </c>
       <c r="W517" t="s">
-        <v>1556</v>
+        <v>1612</v>
       </c>
       <c r="X517" t="s">
         <v>1067</v>
@@ -28668,10 +29070,10 @@
         <v>91</v>
       </c>
       <c r="V518" t="s">
-        <v>1555</v>
+        <v>1613</v>
       </c>
       <c r="W518" t="s">
-        <v>1556</v>
+        <v>1612</v>
       </c>
       <c r="X518" t="s">
         <v>1067</v>
@@ -28682,10 +29084,10 @@
         <v>91</v>
       </c>
       <c r="V519" t="s">
-        <v>1555</v>
+        <v>1614</v>
       </c>
       <c r="W519" t="s">
-        <v>1556</v>
+        <v>1612</v>
       </c>
       <c r="X519" t="s">
         <v>1067</v>
@@ -28696,10 +29098,10 @@
         <v>91</v>
       </c>
       <c r="V520" t="s">
-        <v>1557</v>
+        <v>1615</v>
       </c>
       <c r="W520" t="s">
-        <v>1558</v>
+        <v>1616</v>
       </c>
       <c r="X520" t="s">
         <v>1067</v>
@@ -28710,10 +29112,10 @@
         <v>91</v>
       </c>
       <c r="V521" t="s">
-        <v>1557</v>
+        <v>1617</v>
       </c>
       <c r="W521" t="s">
-        <v>1558</v>
+        <v>1616</v>
       </c>
       <c r="X521" t="s">
         <v>1067</v>
@@ -28724,10 +29126,10 @@
         <v>91</v>
       </c>
       <c r="V522" t="s">
-        <v>1557</v>
+        <v>1618</v>
       </c>
       <c r="W522" t="s">
-        <v>1558</v>
+        <v>1616</v>
       </c>
       <c r="X522" t="s">
         <v>1067</v>
@@ -28738,7 +29140,7 @@
         <v>91</v>
       </c>
       <c r="V523" t="s">
-        <v>1559</v>
+        <v>1619</v>
       </c>
       <c r="W523" t="s">
         <v>986</v>
@@ -28752,7 +29154,7 @@
         <v>91</v>
       </c>
       <c r="V524" t="s">
-        <v>1559</v>
+        <v>1620</v>
       </c>
       <c r="W524" t="s">
         <v>986</v>
@@ -28766,7 +29168,7 @@
         <v>91</v>
       </c>
       <c r="V525" t="s">
-        <v>1559</v>
+        <v>1621</v>
       </c>
       <c r="W525" t="s">
         <v>986</v>
@@ -28780,10 +29182,10 @@
         <v>91</v>
       </c>
       <c r="V526" t="s">
-        <v>1560</v>
+        <v>1622</v>
       </c>
       <c r="W526" t="s">
-        <v>1561</v>
+        <v>1623</v>
       </c>
       <c r="X526" t="s">
         <v>1067</v>
@@ -28794,10 +29196,10 @@
         <v>91</v>
       </c>
       <c r="V527" t="s">
-        <v>1560</v>
+        <v>1624</v>
       </c>
       <c r="W527" t="s">
-        <v>1561</v>
+        <v>1623</v>
       </c>
       <c r="X527" t="s">
         <v>1067</v>
@@ -28808,10 +29210,10 @@
         <v>91</v>
       </c>
       <c r="V528" t="s">
-        <v>1560</v>
+        <v>1625</v>
       </c>
       <c r="W528" t="s">
-        <v>1561</v>
+        <v>1623</v>
       </c>
       <c r="X528" t="s">
         <v>1067</v>
@@ -28822,7 +29224,7 @@
         <v>91</v>
       </c>
       <c r="V529" t="s">
-        <v>1562</v>
+        <v>1626</v>
       </c>
       <c r="W529" t="s">
         <v>1061</v>
@@ -28836,7 +29238,7 @@
         <v>91</v>
       </c>
       <c r="V530" t="s">
-        <v>1562</v>
+        <v>1627</v>
       </c>
       <c r="W530" t="s">
         <v>1061</v>
@@ -28850,7 +29252,7 @@
         <v>91</v>
       </c>
       <c r="V531" t="s">
-        <v>1562</v>
+        <v>1628</v>
       </c>
       <c r="W531" t="s">
         <v>1061</v>
@@ -28864,10 +29266,10 @@
         <v>91</v>
       </c>
       <c r="V532" t="s">
-        <v>1563</v>
+        <v>1629</v>
       </c>
       <c r="W532" t="s">
-        <v>1564</v>
+        <v>1630</v>
       </c>
       <c r="X532" t="s">
         <v>1067</v>
@@ -28878,10 +29280,10 @@
         <v>91</v>
       </c>
       <c r="V533" t="s">
-        <v>1563</v>
+        <v>1631</v>
       </c>
       <c r="W533" t="s">
-        <v>1564</v>
+        <v>1630</v>
       </c>
       <c r="X533" t="s">
         <v>1067</v>
@@ -28892,10 +29294,10 @@
         <v>91</v>
       </c>
       <c r="V534" t="s">
-        <v>1563</v>
+        <v>1632</v>
       </c>
       <c r="W534" t="s">
-        <v>1564</v>
+        <v>1630</v>
       </c>
       <c r="X534" t="s">
         <v>1067</v>
@@ -28906,7 +29308,7 @@
         <v>91</v>
       </c>
       <c r="V535" t="s">
-        <v>1565</v>
+        <v>1633</v>
       </c>
       <c r="W535" t="s">
         <v>1037</v>
@@ -28920,7 +29322,7 @@
         <v>91</v>
       </c>
       <c r="V536" t="s">
-        <v>1565</v>
+        <v>1634</v>
       </c>
       <c r="W536" t="s">
         <v>1037</v>
@@ -28934,7 +29336,7 @@
         <v>91</v>
       </c>
       <c r="V537" t="s">
-        <v>1565</v>
+        <v>1635</v>
       </c>
       <c r="W537" t="s">
         <v>1037</v>
@@ -28948,10 +29350,10 @@
         <v>91</v>
       </c>
       <c r="V538" t="s">
-        <v>1566</v>
+        <v>1636</v>
       </c>
       <c r="W538" t="s">
-        <v>1567</v>
+        <v>1637</v>
       </c>
       <c r="X538" t="s">
         <v>1067</v>
@@ -28962,10 +29364,10 @@
         <v>91</v>
       </c>
       <c r="V539" t="s">
-        <v>1566</v>
+        <v>1638</v>
       </c>
       <c r="W539" t="s">
-        <v>1567</v>
+        <v>1637</v>
       </c>
       <c r="X539" t="s">
         <v>1067</v>
@@ -28976,10 +29378,10 @@
         <v>91</v>
       </c>
       <c r="V540" t="s">
-        <v>1566</v>
+        <v>1639</v>
       </c>
       <c r="W540" t="s">
-        <v>1567</v>
+        <v>1637</v>
       </c>
       <c r="X540" t="s">
         <v>1067</v>
@@ -28990,10 +29392,10 @@
         <v>91</v>
       </c>
       <c r="V541" t="s">
-        <v>1568</v>
+        <v>1640</v>
       </c>
       <c r="W541" t="s">
-        <v>1569</v>
+        <v>1641</v>
       </c>
       <c r="X541" t="s">
         <v>1067</v>
@@ -29004,10 +29406,10 @@
         <v>91</v>
       </c>
       <c r="V542" t="s">
-        <v>1568</v>
+        <v>1642</v>
       </c>
       <c r="W542" t="s">
-        <v>1569</v>
+        <v>1641</v>
       </c>
       <c r="X542" t="s">
         <v>1067</v>
@@ -29018,10 +29420,10 @@
         <v>91</v>
       </c>
       <c r="V543" t="s">
-        <v>1568</v>
+        <v>1643</v>
       </c>
       <c r="W543" t="s">
-        <v>1569</v>
+        <v>1641</v>
       </c>
       <c r="X543" t="s">
         <v>1067</v>
@@ -29032,7 +29434,7 @@
         <v>91</v>
       </c>
       <c r="V544" t="s">
-        <v>1570</v>
+        <v>1644</v>
       </c>
       <c r="W544" t="s">
         <v>1040</v>
@@ -29046,7 +29448,7 @@
         <v>91</v>
       </c>
       <c r="V545" t="s">
-        <v>1570</v>
+        <v>1645</v>
       </c>
       <c r="W545" t="s">
         <v>1040</v>
@@ -29060,7 +29462,7 @@
         <v>91</v>
       </c>
       <c r="V546" t="s">
-        <v>1570</v>
+        <v>1646</v>
       </c>
       <c r="W546" t="s">
         <v>1040</v>
@@ -29074,7 +29476,7 @@
         <v>91</v>
       </c>
       <c r="V547" t="s">
-        <v>1571</v>
+        <v>1647</v>
       </c>
       <c r="W547" t="s">
         <v>1019</v>
@@ -29088,7 +29490,7 @@
         <v>91</v>
       </c>
       <c r="V548" t="s">
-        <v>1571</v>
+        <v>1648</v>
       </c>
       <c r="W548" t="s">
         <v>1019</v>
@@ -29102,7 +29504,7 @@
         <v>91</v>
       </c>
       <c r="V549" t="s">
-        <v>1571</v>
+        <v>1649</v>
       </c>
       <c r="W549" t="s">
         <v>1019</v>
@@ -29116,7 +29518,7 @@
         <v>91</v>
       </c>
       <c r="V550" t="s">
-        <v>1572</v>
+        <v>1650</v>
       </c>
       <c r="W550" t="s">
         <v>970</v>
@@ -29130,7 +29532,7 @@
         <v>91</v>
       </c>
       <c r="V551" t="s">
-        <v>1572</v>
+        <v>1651</v>
       </c>
       <c r="W551" t="s">
         <v>970</v>
@@ -29144,7 +29546,7 @@
         <v>91</v>
       </c>
       <c r="V552" t="s">
-        <v>1572</v>
+        <v>1652</v>
       </c>
       <c r="W552" t="s">
         <v>970</v>
@@ -29158,10 +29560,10 @@
         <v>91</v>
       </c>
       <c r="V553" t="s">
-        <v>1573</v>
+        <v>1653</v>
       </c>
       <c r="W553" t="s">
-        <v>1574</v>
+        <v>1654</v>
       </c>
       <c r="X553" t="s">
         <v>1067</v>
@@ -29172,10 +29574,10 @@
         <v>91</v>
       </c>
       <c r="V554" t="s">
-        <v>1573</v>
+        <v>1655</v>
       </c>
       <c r="W554" t="s">
-        <v>1574</v>
+        <v>1654</v>
       </c>
       <c r="X554" t="s">
         <v>1067</v>
@@ -29186,10 +29588,10 @@
         <v>91</v>
       </c>
       <c r="V555" t="s">
-        <v>1573</v>
+        <v>1656</v>
       </c>
       <c r="W555" t="s">
-        <v>1574</v>
+        <v>1654</v>
       </c>
       <c r="X555" t="s">
         <v>1067</v>
@@ -29200,7 +29602,7 @@
         <v>91</v>
       </c>
       <c r="V556" t="s">
-        <v>1575</v>
+        <v>1657</v>
       </c>
       <c r="W556" t="s">
         <v>1310</v>
@@ -29214,7 +29616,7 @@
         <v>91</v>
       </c>
       <c r="V557" t="s">
-        <v>1575</v>
+        <v>1658</v>
       </c>
       <c r="W557" t="s">
         <v>1310</v>
@@ -29228,7 +29630,7 @@
         <v>91</v>
       </c>
       <c r="V558" t="s">
-        <v>1575</v>
+        <v>1659</v>
       </c>
       <c r="W558" t="s">
         <v>1310</v>
@@ -29242,10 +29644,10 @@
         <v>91</v>
       </c>
       <c r="V559" t="s">
-        <v>1576</v>
+        <v>1660</v>
       </c>
       <c r="W559" t="s">
-        <v>1577</v>
+        <v>1661</v>
       </c>
       <c r="X559" t="s">
         <v>1067</v>
@@ -29256,10 +29658,10 @@
         <v>91</v>
       </c>
       <c r="V560" t="s">
-        <v>1576</v>
+        <v>1662</v>
       </c>
       <c r="W560" t="s">
-        <v>1577</v>
+        <v>1661</v>
       </c>
       <c r="X560" t="s">
         <v>1067</v>
@@ -29270,10 +29672,10 @@
         <v>91</v>
       </c>
       <c r="V561" t="s">
-        <v>1576</v>
+        <v>1663</v>
       </c>
       <c r="W561" t="s">
-        <v>1577</v>
+        <v>1661</v>
       </c>
       <c r="X561" t="s">
         <v>1067</v>
@@ -29284,10 +29686,10 @@
         <v>91</v>
       </c>
       <c r="V562" t="s">
-        <v>1578</v>
+        <v>1664</v>
       </c>
       <c r="W562" t="s">
-        <v>1579</v>
+        <v>1665</v>
       </c>
       <c r="X562" t="s">
         <v>1067</v>
@@ -29298,10 +29700,10 @@
         <v>91</v>
       </c>
       <c r="V563" t="s">
-        <v>1578</v>
+        <v>1666</v>
       </c>
       <c r="W563" t="s">
-        <v>1579</v>
+        <v>1665</v>
       </c>
       <c r="X563" t="s">
         <v>1067</v>
@@ -29312,10 +29714,10 @@
         <v>91</v>
       </c>
       <c r="V564" t="s">
-        <v>1578</v>
+        <v>1667</v>
       </c>
       <c r="W564" t="s">
-        <v>1579</v>
+        <v>1665</v>
       </c>
       <c r="X564" t="s">
         <v>1067</v>
@@ -29326,10 +29728,10 @@
         <v>91</v>
       </c>
       <c r="V565" t="s">
-        <v>1580</v>
+        <v>1668</v>
       </c>
       <c r="W565" t="s">
-        <v>1581</v>
+        <v>1669</v>
       </c>
       <c r="X565" t="s">
         <v>1067</v>
@@ -29340,10 +29742,10 @@
         <v>91</v>
       </c>
       <c r="V566" t="s">
-        <v>1580</v>
+        <v>1670</v>
       </c>
       <c r="W566" t="s">
-        <v>1581</v>
+        <v>1669</v>
       </c>
       <c r="X566" t="s">
         <v>1067</v>
@@ -29354,10 +29756,10 @@
         <v>91</v>
       </c>
       <c r="V567" t="s">
-        <v>1580</v>
+        <v>1671</v>
       </c>
       <c r="W567" t="s">
-        <v>1581</v>
+        <v>1669</v>
       </c>
       <c r="X567" t="s">
         <v>1067</v>
@@ -29368,10 +29770,10 @@
         <v>91</v>
       </c>
       <c r="V568" t="s">
-        <v>1582</v>
+        <v>1672</v>
       </c>
       <c r="W568" t="s">
-        <v>1583</v>
+        <v>1673</v>
       </c>
       <c r="X568" t="s">
         <v>1067</v>
@@ -29382,10 +29784,10 @@
         <v>91</v>
       </c>
       <c r="V569" t="s">
-        <v>1582</v>
+        <v>1674</v>
       </c>
       <c r="W569" t="s">
-        <v>1583</v>
+        <v>1673</v>
       </c>
       <c r="X569" t="s">
         <v>1067</v>
@@ -29396,10 +29798,10 @@
         <v>91</v>
       </c>
       <c r="V570" t="s">
-        <v>1582</v>
+        <v>1675</v>
       </c>
       <c r="W570" t="s">
-        <v>1583</v>
+        <v>1673</v>
       </c>
       <c r="X570" t="s">
         <v>1067</v>
@@ -29410,7 +29812,7 @@
         <v>91</v>
       </c>
       <c r="V571" t="s">
-        <v>1584</v>
+        <v>1676</v>
       </c>
       <c r="W571" t="s">
         <v>1060</v>
@@ -29424,7 +29826,7 @@
         <v>91</v>
       </c>
       <c r="V572" t="s">
-        <v>1584</v>
+        <v>1677</v>
       </c>
       <c r="W572" t="s">
         <v>1060</v>
@@ -29438,7 +29840,7 @@
         <v>91</v>
       </c>
       <c r="V573" t="s">
-        <v>1584</v>
+        <v>1678</v>
       </c>
       <c r="W573" t="s">
         <v>1060</v>
@@ -29452,10 +29854,10 @@
         <v>91</v>
       </c>
       <c r="V574" t="s">
-        <v>1585</v>
+        <v>1679</v>
       </c>
       <c r="W574" t="s">
-        <v>1586</v>
+        <v>1680</v>
       </c>
       <c r="X574" t="s">
         <v>1067</v>
@@ -29466,10 +29868,10 @@
         <v>91</v>
       </c>
       <c r="V575" t="s">
-        <v>1585</v>
+        <v>1681</v>
       </c>
       <c r="W575" t="s">
-        <v>1586</v>
+        <v>1680</v>
       </c>
       <c r="X575" t="s">
         <v>1067</v>
@@ -29480,10 +29882,10 @@
         <v>91</v>
       </c>
       <c r="V576" t="s">
-        <v>1585</v>
+        <v>1682</v>
       </c>
       <c r="W576" t="s">
-        <v>1586</v>
+        <v>1680</v>
       </c>
       <c r="X576" t="s">
         <v>1067</v>
@@ -29494,10 +29896,10 @@
         <v>91</v>
       </c>
       <c r="V577" t="s">
-        <v>1587</v>
+        <v>1683</v>
       </c>
       <c r="W577" t="s">
-        <v>1588</v>
+        <v>1684</v>
       </c>
       <c r="X577" t="s">
         <v>1067</v>
@@ -29508,10 +29910,10 @@
         <v>91</v>
       </c>
       <c r="V578" t="s">
-        <v>1587</v>
+        <v>1685</v>
       </c>
       <c r="W578" t="s">
-        <v>1588</v>
+        <v>1684</v>
       </c>
       <c r="X578" t="s">
         <v>1067</v>
@@ -29522,10 +29924,10 @@
         <v>91</v>
       </c>
       <c r="V579" t="s">
-        <v>1587</v>
+        <v>1686</v>
       </c>
       <c r="W579" t="s">
-        <v>1588</v>
+        <v>1684</v>
       </c>
       <c r="X579" t="s">
         <v>1067</v>
@@ -29536,7 +29938,7 @@
         <v>91</v>
       </c>
       <c r="V580" t="s">
-        <v>1589</v>
+        <v>1687</v>
       </c>
       <c r="W580" t="s">
         <v>1016</v>
@@ -29550,7 +29952,7 @@
         <v>91</v>
       </c>
       <c r="V581" t="s">
-        <v>1589</v>
+        <v>1688</v>
       </c>
       <c r="W581" t="s">
         <v>1016</v>
@@ -29564,7 +29966,7 @@
         <v>91</v>
       </c>
       <c r="V582" t="s">
-        <v>1589</v>
+        <v>1689</v>
       </c>
       <c r="W582" t="s">
         <v>1016</v>
@@ -29578,10 +29980,10 @@
         <v>91</v>
       </c>
       <c r="V583" t="s">
-        <v>1590</v>
+        <v>1690</v>
       </c>
       <c r="W583" t="s">
-        <v>1591</v>
+        <v>1691</v>
       </c>
       <c r="X583" t="s">
         <v>1067</v>
@@ -29592,10 +29994,10 @@
         <v>91</v>
       </c>
       <c r="V584" t="s">
-        <v>1590</v>
+        <v>1692</v>
       </c>
       <c r="W584" t="s">
-        <v>1591</v>
+        <v>1691</v>
       </c>
       <c r="X584" t="s">
         <v>1067</v>
@@ -29606,10 +30008,10 @@
         <v>91</v>
       </c>
       <c r="V585" t="s">
-        <v>1590</v>
+        <v>1693</v>
       </c>
       <c r="W585" t="s">
-        <v>1591</v>
+        <v>1691</v>
       </c>
       <c r="X585" t="s">
         <v>1067</v>
@@ -29620,7 +30022,7 @@
         <v>91</v>
       </c>
       <c r="V586" t="s">
-        <v>1592</v>
+        <v>1694</v>
       </c>
       <c r="W586" t="s">
         <v>994</v>
@@ -29634,7 +30036,7 @@
         <v>91</v>
       </c>
       <c r="V587" t="s">
-        <v>1592</v>
+        <v>1695</v>
       </c>
       <c r="W587" t="s">
         <v>994</v>
@@ -29648,7 +30050,7 @@
         <v>91</v>
       </c>
       <c r="V588" t="s">
-        <v>1592</v>
+        <v>1696</v>
       </c>
       <c r="W588" t="s">
         <v>994</v>
@@ -29662,10 +30064,10 @@
         <v>91</v>
       </c>
       <c r="V589" t="s">
-        <v>1593</v>
+        <v>1697</v>
       </c>
       <c r="W589" t="s">
-        <v>1594</v>
+        <v>1698</v>
       </c>
       <c r="X589" t="s">
         <v>1067</v>
@@ -29676,10 +30078,10 @@
         <v>91</v>
       </c>
       <c r="V590" t="s">
-        <v>1593</v>
+        <v>1699</v>
       </c>
       <c r="W590" t="s">
-        <v>1594</v>
+        <v>1698</v>
       </c>
       <c r="X590" t="s">
         <v>1067</v>
@@ -29690,10 +30092,10 @@
         <v>91</v>
       </c>
       <c r="V591" t="s">
-        <v>1593</v>
+        <v>1700</v>
       </c>
       <c r="W591" t="s">
-        <v>1594</v>
+        <v>1698</v>
       </c>
       <c r="X591" t="s">
         <v>1067</v>
@@ -29704,10 +30106,10 @@
         <v>91</v>
       </c>
       <c r="V592" t="s">
-        <v>1595</v>
+        <v>1701</v>
       </c>
       <c r="W592" t="s">
-        <v>1596</v>
+        <v>1702</v>
       </c>
       <c r="X592" t="s">
         <v>1067</v>
@@ -29718,10 +30120,10 @@
         <v>91</v>
       </c>
       <c r="V593" t="s">
-        <v>1595</v>
+        <v>1703</v>
       </c>
       <c r="W593" t="s">
-        <v>1596</v>
+        <v>1702</v>
       </c>
       <c r="X593" t="s">
         <v>1067</v>
@@ -29732,10 +30134,10 @@
         <v>91</v>
       </c>
       <c r="V594" t="s">
-        <v>1595</v>
+        <v>1704</v>
       </c>
       <c r="W594" t="s">
-        <v>1596</v>
+        <v>1702</v>
       </c>
       <c r="X594" t="s">
         <v>1067</v>
@@ -29746,10 +30148,10 @@
         <v>91</v>
       </c>
       <c r="V595" t="s">
-        <v>1597</v>
+        <v>1705</v>
       </c>
       <c r="W595" t="s">
-        <v>1598</v>
+        <v>1706</v>
       </c>
       <c r="X595" t="s">
         <v>1067</v>
@@ -29760,10 +30162,10 @@
         <v>91</v>
       </c>
       <c r="V596" t="s">
-        <v>1597</v>
+        <v>1707</v>
       </c>
       <c r="W596" t="s">
-        <v>1598</v>
+        <v>1706</v>
       </c>
       <c r="X596" t="s">
         <v>1067</v>
@@ -29774,10 +30176,10 @@
         <v>91</v>
       </c>
       <c r="V597" t="s">
-        <v>1597</v>
+        <v>1708</v>
       </c>
       <c r="W597" t="s">
-        <v>1598</v>
+        <v>1706</v>
       </c>
       <c r="X597" t="s">
         <v>1067</v>
@@ -29788,7 +30190,7 @@
         <v>91</v>
       </c>
       <c r="V598" t="s">
-        <v>1599</v>
+        <v>1709</v>
       </c>
       <c r="W598" t="s">
         <v>1017</v>
@@ -29802,7 +30204,7 @@
         <v>91</v>
       </c>
       <c r="V599" t="s">
-        <v>1599</v>
+        <v>1710</v>
       </c>
       <c r="W599" t="s">
         <v>1017</v>
@@ -29816,7 +30218,7 @@
         <v>91</v>
       </c>
       <c r="V600" t="s">
-        <v>1599</v>
+        <v>1711</v>
       </c>
       <c r="W600" t="s">
         <v>1017</v>
@@ -29830,10 +30232,10 @@
         <v>91</v>
       </c>
       <c r="V601" t="s">
-        <v>1600</v>
+        <v>1712</v>
       </c>
       <c r="W601" t="s">
-        <v>1601</v>
+        <v>1713</v>
       </c>
       <c r="X601" t="s">
         <v>1067</v>
@@ -29844,10 +30246,10 @@
         <v>91</v>
       </c>
       <c r="V602" t="s">
-        <v>1600</v>
+        <v>1714</v>
       </c>
       <c r="W602" t="s">
-        <v>1601</v>
+        <v>1713</v>
       </c>
       <c r="X602" t="s">
         <v>1067</v>
@@ -29858,10 +30260,10 @@
         <v>91</v>
       </c>
       <c r="V603" t="s">
-        <v>1600</v>
+        <v>1715</v>
       </c>
       <c r="W603" t="s">
-        <v>1601</v>
+        <v>1713</v>
       </c>
       <c r="X603" t="s">
         <v>1067</v>
@@ -29872,10 +30274,10 @@
         <v>91</v>
       </c>
       <c r="V604" t="s">
-        <v>1602</v>
+        <v>1716</v>
       </c>
       <c r="W604" t="s">
-        <v>1603</v>
+        <v>1717</v>
       </c>
       <c r="X604" t="s">
         <v>1067</v>
@@ -29886,10 +30288,10 @@
         <v>91</v>
       </c>
       <c r="V605" t="s">
-        <v>1602</v>
+        <v>1718</v>
       </c>
       <c r="W605" t="s">
-        <v>1603</v>
+        <v>1717</v>
       </c>
       <c r="X605" t="s">
         <v>1067</v>
@@ -29900,10 +30302,10 @@
         <v>91</v>
       </c>
       <c r="V606" t="s">
-        <v>1602</v>
+        <v>1719</v>
       </c>
       <c r="W606" t="s">
-        <v>1603</v>
+        <v>1717</v>
       </c>
       <c r="X606" t="s">
         <v>1067</v>
@@ -29914,10 +30316,10 @@
         <v>91</v>
       </c>
       <c r="V607" t="s">
-        <v>1604</v>
+        <v>1720</v>
       </c>
       <c r="W607" t="s">
-        <v>1605</v>
+        <v>1721</v>
       </c>
       <c r="X607" t="s">
         <v>1067</v>
@@ -29928,10 +30330,10 @@
         <v>91</v>
       </c>
       <c r="V608" t="s">
-        <v>1604</v>
+        <v>1722</v>
       </c>
       <c r="W608" t="s">
-        <v>1605</v>
+        <v>1721</v>
       </c>
       <c r="X608" t="s">
         <v>1067</v>
@@ -29942,10 +30344,10 @@
         <v>91</v>
       </c>
       <c r="V609" t="s">
-        <v>1604</v>
+        <v>1723</v>
       </c>
       <c r="W609" t="s">
-        <v>1605</v>
+        <v>1721</v>
       </c>
       <c r="X609" t="s">
         <v>1067</v>
@@ -29956,10 +30358,10 @@
         <v>91</v>
       </c>
       <c r="V610" t="s">
-        <v>1606</v>
+        <v>1724</v>
       </c>
       <c r="W610" t="s">
-        <v>1607</v>
+        <v>1725</v>
       </c>
       <c r="X610" t="s">
         <v>1067</v>
@@ -29970,10 +30372,10 @@
         <v>91</v>
       </c>
       <c r="V611" t="s">
-        <v>1606</v>
+        <v>1726</v>
       </c>
       <c r="W611" t="s">
-        <v>1607</v>
+        <v>1725</v>
       </c>
       <c r="X611" t="s">
         <v>1067</v>
@@ -29984,10 +30386,10 @@
         <v>91</v>
       </c>
       <c r="V612" t="s">
-        <v>1606</v>
+        <v>1727</v>
       </c>
       <c r="W612" t="s">
-        <v>1607</v>
+        <v>1725</v>
       </c>
       <c r="X612" t="s">
         <v>1067</v>
@@ -29998,10 +30400,10 @@
         <v>91</v>
       </c>
       <c r="V613" t="s">
-        <v>1608</v>
+        <v>1728</v>
       </c>
       <c r="W613" t="s">
-        <v>1609</v>
+        <v>1729</v>
       </c>
       <c r="X613" t="s">
         <v>1067</v>
@@ -30012,10 +30414,10 @@
         <v>91</v>
       </c>
       <c r="V614" t="s">
-        <v>1608</v>
+        <v>1730</v>
       </c>
       <c r="W614" t="s">
-        <v>1609</v>
+        <v>1729</v>
       </c>
       <c r="X614" t="s">
         <v>1067</v>
@@ -30026,10 +30428,10 @@
         <v>91</v>
       </c>
       <c r="V615" t="s">
-        <v>1608</v>
+        <v>1731</v>
       </c>
       <c r="W615" t="s">
-        <v>1609</v>
+        <v>1729</v>
       </c>
       <c r="X615" t="s">
         <v>1067</v>
@@ -30040,10 +30442,10 @@
         <v>91</v>
       </c>
       <c r="V616" t="s">
-        <v>1610</v>
+        <v>1732</v>
       </c>
       <c r="W616" t="s">
-        <v>1611</v>
+        <v>1733</v>
       </c>
       <c r="X616" t="s">
         <v>1067</v>
@@ -30054,10 +30456,10 @@
         <v>91</v>
       </c>
       <c r="V617" t="s">
-        <v>1610</v>
+        <v>1734</v>
       </c>
       <c r="W617" t="s">
-        <v>1611</v>
+        <v>1733</v>
       </c>
       <c r="X617" t="s">
         <v>1067</v>
@@ -30068,10 +30470,10 @@
         <v>91</v>
       </c>
       <c r="V618" t="s">
-        <v>1610</v>
+        <v>1735</v>
       </c>
       <c r="W618" t="s">
-        <v>1611</v>
+        <v>1733</v>
       </c>
       <c r="X618" t="s">
         <v>1067</v>
@@ -30082,10 +30484,10 @@
         <v>91</v>
       </c>
       <c r="V619" t="s">
-        <v>1612</v>
+        <v>1736</v>
       </c>
       <c r="W619" t="s">
-        <v>1613</v>
+        <v>1737</v>
       </c>
       <c r="X619" t="s">
         <v>1067</v>
@@ -30096,10 +30498,10 @@
         <v>91</v>
       </c>
       <c r="V620" t="s">
-        <v>1612</v>
+        <v>1738</v>
       </c>
       <c r="W620" t="s">
-        <v>1613</v>
+        <v>1737</v>
       </c>
       <c r="X620" t="s">
         <v>1067</v>
@@ -30110,10 +30512,10 @@
         <v>91</v>
       </c>
       <c r="V621" t="s">
-        <v>1612</v>
+        <v>1739</v>
       </c>
       <c r="W621" t="s">
-        <v>1613</v>
+        <v>1737</v>
       </c>
       <c r="X621" t="s">
         <v>1067</v>
@@ -30124,10 +30526,10 @@
         <v>91</v>
       </c>
       <c r="V622" t="s">
-        <v>1614</v>
+        <v>1740</v>
       </c>
       <c r="W622" t="s">
-        <v>1615</v>
+        <v>1741</v>
       </c>
       <c r="X622" t="s">
         <v>1067</v>
@@ -30138,10 +30540,10 @@
         <v>91</v>
       </c>
       <c r="V623" t="s">
-        <v>1614</v>
+        <v>1742</v>
       </c>
       <c r="W623" t="s">
-        <v>1615</v>
+        <v>1741</v>
       </c>
       <c r="X623" t="s">
         <v>1067</v>
@@ -30152,10 +30554,10 @@
         <v>91</v>
       </c>
       <c r="V624" t="s">
-        <v>1614</v>
+        <v>1743</v>
       </c>
       <c r="W624" t="s">
-        <v>1615</v>
+        <v>1741</v>
       </c>
       <c r="X624" t="s">
         <v>1067</v>
@@ -30166,10 +30568,10 @@
         <v>91</v>
       </c>
       <c r="V625" t="s">
-        <v>1616</v>
+        <v>1744</v>
       </c>
       <c r="W625" t="s">
-        <v>1617</v>
+        <v>1745</v>
       </c>
       <c r="X625" t="s">
         <v>1067</v>
@@ -30180,10 +30582,10 @@
         <v>91</v>
       </c>
       <c r="V626" t="s">
-        <v>1616</v>
+        <v>1746</v>
       </c>
       <c r="W626" t="s">
-        <v>1617</v>
+        <v>1745</v>
       </c>
       <c r="X626" t="s">
         <v>1067</v>
@@ -30194,10 +30596,10 @@
         <v>91</v>
       </c>
       <c r="V627" t="s">
-        <v>1616</v>
+        <v>1747</v>
       </c>
       <c r="W627" t="s">
-        <v>1617</v>
+        <v>1745</v>
       </c>
       <c r="X627" t="s">
         <v>1067</v>
@@ -30208,10 +30610,10 @@
         <v>91</v>
       </c>
       <c r="V628" t="s">
-        <v>1618</v>
+        <v>1748</v>
       </c>
       <c r="W628" t="s">
-        <v>1619</v>
+        <v>1749</v>
       </c>
       <c r="X628" t="s">
         <v>1067</v>
@@ -30222,10 +30624,10 @@
         <v>91</v>
       </c>
       <c r="V629" t="s">
-        <v>1618</v>
+        <v>1750</v>
       </c>
       <c r="W629" t="s">
-        <v>1619</v>
+        <v>1749</v>
       </c>
       <c r="X629" t="s">
         <v>1067</v>
@@ -30236,10 +30638,10 @@
         <v>91</v>
       </c>
       <c r="V630" t="s">
-        <v>1618</v>
+        <v>1751</v>
       </c>
       <c r="W630" t="s">
-        <v>1619</v>
+        <v>1749</v>
       </c>
       <c r="X630" t="s">
         <v>1067</v>
@@ -30250,7 +30652,7 @@
         <v>91</v>
       </c>
       <c r="V631" t="s">
-        <v>1620</v>
+        <v>1752</v>
       </c>
       <c r="W631" t="s">
         <v>1010</v>
@@ -30264,7 +30666,7 @@
         <v>91</v>
       </c>
       <c r="V632" t="s">
-        <v>1620</v>
+        <v>1753</v>
       </c>
       <c r="W632" t="s">
         <v>1010</v>
@@ -30278,7 +30680,7 @@
         <v>91</v>
       </c>
       <c r="V633" t="s">
-        <v>1620</v>
+        <v>1754</v>
       </c>
       <c r="W633" t="s">
         <v>1010</v>
@@ -30292,7 +30694,7 @@
         <v>91</v>
       </c>
       <c r="V634" t="s">
-        <v>1621</v>
+        <v>1755</v>
       </c>
       <c r="W634" t="s">
         <v>1066</v>
@@ -30306,7 +30708,7 @@
         <v>91</v>
       </c>
       <c r="V635" t="s">
-        <v>1622</v>
+        <v>1756</v>
       </c>
       <c r="W635" t="s">
         <v>1066</v>
@@ -30320,10 +30722,10 @@
         <v>91</v>
       </c>
       <c r="V636" t="s">
-        <v>1623</v>
+        <v>1757</v>
       </c>
       <c r="W636" t="s">
-        <v>1624</v>
+        <v>1758</v>
       </c>
       <c r="X636" t="s">
         <v>1067</v>
@@ -30334,10 +30736,10 @@
         <v>91</v>
       </c>
       <c r="V637" t="s">
-        <v>1625</v>
+        <v>1759</v>
       </c>
       <c r="W637" t="s">
-        <v>1624</v>
+        <v>1758</v>
       </c>
       <c r="X637" t="s">
         <v>1067</v>
@@ -30348,7 +30750,7 @@
         <v>91</v>
       </c>
       <c r="V638" t="s">
-        <v>1626</v>
+        <v>1760</v>
       </c>
       <c r="W638" t="s">
         <v>1050</v>
@@ -30362,7 +30764,7 @@
         <v>91</v>
       </c>
       <c r="V639" t="s">
-        <v>1627</v>
+        <v>1761</v>
       </c>
       <c r="W639" t="s">
         <v>1050</v>
@@ -30376,7 +30778,7 @@
         <v>91</v>
       </c>
       <c r="V640" t="s">
-        <v>1628</v>
+        <v>1762</v>
       </c>
       <c r="W640" t="s">
         <v>994</v>
@@ -30390,7 +30792,7 @@
         <v>91</v>
       </c>
       <c r="V641" t="s">
-        <v>1629</v>
+        <v>1763</v>
       </c>
       <c r="W641" t="s">
         <v>994</v>
@@ -30404,7 +30806,7 @@
         <v>91</v>
       </c>
       <c r="V642" t="s">
-        <v>1630</v>
+        <v>1764</v>
       </c>
       <c r="W642" t="s">
         <v>1060</v>
@@ -30418,7 +30820,7 @@
         <v>91</v>
       </c>
       <c r="V643" t="s">
-        <v>1631</v>
+        <v>1765</v>
       </c>
       <c r="W643" t="s">
         <v>1060</v>
@@ -30432,7 +30834,7 @@
         <v>91</v>
       </c>
       <c r="V644" t="s">
-        <v>1632</v>
+        <v>1766</v>
       </c>
       <c r="W644" t="s">
         <v>1014</v>
@@ -30446,7 +30848,7 @@
         <v>91</v>
       </c>
       <c r="V645" t="s">
-        <v>1633</v>
+        <v>1767</v>
       </c>
       <c r="W645" t="s">
         <v>1014</v>
@@ -30460,10 +30862,10 @@
         <v>91</v>
       </c>
       <c r="V646" t="s">
-        <v>1634</v>
+        <v>1768</v>
       </c>
       <c r="W646" t="s">
-        <v>1635</v>
+        <v>1769</v>
       </c>
       <c r="X646" t="s">
         <v>1067</v>
@@ -30474,10 +30876,10 @@
         <v>91</v>
       </c>
       <c r="V647" t="s">
-        <v>1636</v>
+        <v>1770</v>
       </c>
       <c r="W647" t="s">
-        <v>1635</v>
+        <v>1769</v>
       </c>
       <c r="X647" t="s">
         <v>1067</v>
@@ -30488,7 +30890,7 @@
         <v>91</v>
       </c>
       <c r="V648" t="s">
-        <v>1637</v>
+        <v>1771</v>
       </c>
       <c r="W648" t="s">
         <v>1175</v>
@@ -30502,7 +30904,7 @@
         <v>91</v>
       </c>
       <c r="V649" t="s">
-        <v>1638</v>
+        <v>1772</v>
       </c>
       <c r="W649" t="s">
         <v>1175</v>
@@ -30516,7 +30918,7 @@
         <v>91</v>
       </c>
       <c r="V650" t="s">
-        <v>1639</v>
+        <v>1773</v>
       </c>
       <c r="W650" t="s">
         <v>1020</v>
@@ -30530,7 +30932,7 @@
         <v>91</v>
       </c>
       <c r="V651" t="s">
-        <v>1640</v>
+        <v>1774</v>
       </c>
       <c r="W651" t="s">
         <v>1020</v>
@@ -30544,10 +30946,10 @@
         <v>91</v>
       </c>
       <c r="V652" t="s">
-        <v>1641</v>
+        <v>1775</v>
       </c>
       <c r="W652" t="s">
-        <v>1642</v>
+        <v>1776</v>
       </c>
       <c r="X652" t="s">
         <v>1067</v>
@@ -30558,10 +30960,10 @@
         <v>91</v>
       </c>
       <c r="V653" t="s">
-        <v>1643</v>
+        <v>1777</v>
       </c>
       <c r="W653" t="s">
-        <v>1642</v>
+        <v>1776</v>
       </c>
       <c r="X653" t="s">
         <v>1067</v>
@@ -30572,10 +30974,10 @@
         <v>91</v>
       </c>
       <c r="V654" t="s">
-        <v>1644</v>
+        <v>1778</v>
       </c>
       <c r="W654" t="s">
-        <v>1645</v>
+        <v>1779</v>
       </c>
       <c r="X654" t="s">
         <v>1067</v>
@@ -30586,10 +30988,10 @@
         <v>91</v>
       </c>
       <c r="V655" t="s">
-        <v>1646</v>
+        <v>1780</v>
       </c>
       <c r="W655" t="s">
-        <v>1645</v>
+        <v>1779</v>
       </c>
       <c r="X655" t="s">
         <v>1067</v>
@@ -30600,10 +31002,10 @@
         <v>91</v>
       </c>
       <c r="V656" t="s">
-        <v>1647</v>
+        <v>1781</v>
       </c>
       <c r="W656" t="s">
-        <v>1561</v>
+        <v>1623</v>
       </c>
       <c r="X656" t="s">
         <v>1067</v>
@@ -30614,10 +31016,10 @@
         <v>91</v>
       </c>
       <c r="V657" t="s">
-        <v>1648</v>
+        <v>1782</v>
       </c>
       <c r="W657" t="s">
-        <v>1561</v>
+        <v>1623</v>
       </c>
       <c r="X657" t="s">
         <v>1067</v>
@@ -30628,7 +31030,7 @@
         <v>91</v>
       </c>
       <c r="V658" t="s">
-        <v>1649</v>
+        <v>1783</v>
       </c>
       <c r="W658" t="s">
         <v>1042</v>
@@ -30642,7 +31044,7 @@
         <v>91</v>
       </c>
       <c r="V659" t="s">
-        <v>1650</v>
+        <v>1784</v>
       </c>
       <c r="W659" t="s">
         <v>1042</v>
@@ -30656,7 +31058,7 @@
         <v>91</v>
       </c>
       <c r="V660" t="s">
-        <v>1651</v>
+        <v>1785</v>
       </c>
       <c r="W660" t="s">
         <v>1011</v>
@@ -30670,7 +31072,7 @@
         <v>91</v>
       </c>
       <c r="V661" t="s">
-        <v>1652</v>
+        <v>1786</v>
       </c>
       <c r="W661" t="s">
         <v>1011</v>
@@ -30684,7 +31086,7 @@
         <v>91</v>
       </c>
       <c r="V662" t="s">
-        <v>1653</v>
+        <v>1787</v>
       </c>
       <c r="W662" t="s">
         <v>1015</v>
@@ -30698,7 +31100,7 @@
         <v>91</v>
       </c>
       <c r="V663" t="s">
-        <v>1654</v>
+        <v>1788</v>
       </c>
       <c r="W663" t="s">
         <v>1015</v>
@@ -30712,10 +31114,10 @@
         <v>91</v>
       </c>
       <c r="V664" t="s">
-        <v>1655</v>
+        <v>1789</v>
       </c>
       <c r="W664" t="s">
-        <v>1656</v>
+        <v>1790</v>
       </c>
       <c r="X664" t="s">
         <v>1067</v>
@@ -30726,10 +31128,10 @@
         <v>91</v>
       </c>
       <c r="V665" t="s">
-        <v>1657</v>
+        <v>1791</v>
       </c>
       <c r="W665" t="s">
-        <v>1656</v>
+        <v>1790</v>
       </c>
       <c r="X665" t="s">
         <v>1067</v>
@@ -30740,10 +31142,10 @@
         <v>91</v>
       </c>
       <c r="V666" t="s">
-        <v>1658</v>
+        <v>1792</v>
       </c>
       <c r="W666" t="s">
-        <v>1659</v>
+        <v>1793</v>
       </c>
       <c r="X666" t="s">
         <v>1067</v>
@@ -30754,10 +31156,10 @@
         <v>91</v>
       </c>
       <c r="V667" t="s">
-        <v>1660</v>
+        <v>1794</v>
       </c>
       <c r="W667" t="s">
-        <v>1659</v>
+        <v>1793</v>
       </c>
       <c r="X667" t="s">
         <v>1067</v>
@@ -30768,10 +31170,10 @@
         <v>91</v>
       </c>
       <c r="V668" t="s">
-        <v>1661</v>
+        <v>1795</v>
       </c>
       <c r="W668" t="s">
-        <v>1662</v>
+        <v>1796</v>
       </c>
       <c r="X668" t="s">
         <v>1067</v>
@@ -30782,10 +31184,10 @@
         <v>91</v>
       </c>
       <c r="V669" t="s">
-        <v>1663</v>
+        <v>1797</v>
       </c>
       <c r="W669" t="s">
-        <v>1662</v>
+        <v>1796</v>
       </c>
       <c r="X669" t="s">
         <v>1067</v>
@@ -30796,10 +31198,10 @@
         <v>91</v>
       </c>
       <c r="V670" t="s">
-        <v>1664</v>
+        <v>1798</v>
       </c>
       <c r="W670" t="s">
-        <v>1665</v>
+        <v>1799</v>
       </c>
       <c r="X670" t="s">
         <v>1067</v>
@@ -30810,10 +31212,10 @@
         <v>91</v>
       </c>
       <c r="V671" t="s">
-        <v>1666</v>
+        <v>1800</v>
       </c>
       <c r="W671" t="s">
-        <v>1665</v>
+        <v>1799</v>
       </c>
       <c r="X671" t="s">
         <v>1067</v>
@@ -30824,10 +31226,10 @@
         <v>91</v>
       </c>
       <c r="V672" t="s">
-        <v>1667</v>
+        <v>1801</v>
       </c>
       <c r="W672" t="s">
-        <v>1611</v>
+        <v>1733</v>
       </c>
       <c r="X672" t="s">
         <v>1067</v>
@@ -30838,10 +31240,10 @@
         <v>91</v>
       </c>
       <c r="V673" t="s">
-        <v>1668</v>
+        <v>1802</v>
       </c>
       <c r="W673" t="s">
-        <v>1611</v>
+        <v>1733</v>
       </c>
       <c r="X673" t="s">
         <v>1067</v>
@@ -30852,7 +31254,7 @@
         <v>91</v>
       </c>
       <c r="V674" t="s">
-        <v>1669</v>
+        <v>1803</v>
       </c>
       <c r="W674" t="s">
         <v>1054</v>
@@ -30866,7 +31268,7 @@
         <v>91</v>
       </c>
       <c r="V675" t="s">
-        <v>1670</v>
+        <v>1804</v>
       </c>
       <c r="W675" t="s">
         <v>1054</v>
@@ -30880,10 +31282,10 @@
         <v>91</v>
       </c>
       <c r="V676" t="s">
-        <v>1671</v>
+        <v>1805</v>
       </c>
       <c r="W676" t="s">
-        <v>1672</v>
+        <v>1806</v>
       </c>
       <c r="X676" t="s">
         <v>1067</v>
@@ -30894,10 +31296,10 @@
         <v>91</v>
       </c>
       <c r="V677" t="s">
-        <v>1673</v>
+        <v>1807</v>
       </c>
       <c r="W677" t="s">
-        <v>1672</v>
+        <v>1806</v>
       </c>
       <c r="X677" t="s">
         <v>1067</v>
@@ -30908,7 +31310,7 @@
         <v>91</v>
       </c>
       <c r="V678" t="s">
-        <v>1674</v>
+        <v>1808</v>
       </c>
       <c r="W678" t="s">
         <v>972</v>
@@ -30922,7 +31324,7 @@
         <v>91</v>
       </c>
       <c r="V679" t="s">
-        <v>1675</v>
+        <v>1809</v>
       </c>
       <c r="W679" t="s">
         <v>972</v>
@@ -30936,7 +31338,7 @@
         <v>91</v>
       </c>
       <c r="V680" t="s">
-        <v>1676</v>
+        <v>1810</v>
       </c>
       <c r="W680" t="s">
         <v>996</v>
@@ -30950,7 +31352,7 @@
         <v>91</v>
       </c>
       <c r="V681" t="s">
-        <v>1677</v>
+        <v>1811</v>
       </c>
       <c r="W681" t="s">
         <v>996</v>
@@ -30964,10 +31366,10 @@
         <v>91</v>
       </c>
       <c r="V682" t="s">
-        <v>1678</v>
+        <v>1812</v>
       </c>
       <c r="W682" t="s">
-        <v>1679</v>
+        <v>1813</v>
       </c>
       <c r="X682" t="s">
         <v>1067</v>
@@ -30978,10 +31380,10 @@
         <v>91</v>
       </c>
       <c r="V683" t="s">
-        <v>1680</v>
+        <v>1814</v>
       </c>
       <c r="W683" t="s">
-        <v>1679</v>
+        <v>1813</v>
       </c>
       <c r="X683" t="s">
         <v>1067</v>
@@ -30992,10 +31394,10 @@
         <v>91</v>
       </c>
       <c r="V684" t="s">
-        <v>1681</v>
+        <v>1815</v>
       </c>
       <c r="W684" t="s">
-        <v>1682</v>
+        <v>1816</v>
       </c>
       <c r="X684" t="s">
         <v>1067</v>
@@ -31006,10 +31408,10 @@
         <v>91</v>
       </c>
       <c r="V685" t="s">
-        <v>1683</v>
+        <v>1817</v>
       </c>
       <c r="W685" t="s">
-        <v>1682</v>
+        <v>1816</v>
       </c>
       <c r="X685" t="s">
         <v>1067</v>
@@ -31020,10 +31422,10 @@
         <v>91</v>
       </c>
       <c r="V686" t="s">
-        <v>1684</v>
+        <v>1818</v>
       </c>
       <c r="W686" t="s">
-        <v>1583</v>
+        <v>1673</v>
       </c>
       <c r="X686" t="s">
         <v>1067</v>
@@ -31034,10 +31436,10 @@
         <v>91</v>
       </c>
       <c r="V687" t="s">
-        <v>1685</v>
+        <v>1819</v>
       </c>
       <c r="W687" t="s">
-        <v>1583</v>
+        <v>1673</v>
       </c>
       <c r="X687" t="s">
         <v>1067</v>
@@ -31048,10 +31450,10 @@
         <v>91</v>
       </c>
       <c r="V688" t="s">
-        <v>1686</v>
+        <v>1820</v>
       </c>
       <c r="W688" t="s">
-        <v>1522</v>
+        <v>1536</v>
       </c>
       <c r="X688" t="s">
         <v>1067</v>
@@ -31062,10 +31464,10 @@
         <v>91</v>
       </c>
       <c r="V689" t="s">
-        <v>1687</v>
+        <v>1821</v>
       </c>
       <c r="W689" t="s">
-        <v>1522</v>
+        <v>1536</v>
       </c>
       <c r="X689" t="s">
         <v>1067</v>
@@ -31076,7 +31478,7 @@
         <v>91</v>
       </c>
       <c r="V690" t="s">
-        <v>1688</v>
+        <v>1822</v>
       </c>
       <c r="W690" t="s">
         <v>988</v>
@@ -31090,7 +31492,7 @@
         <v>91</v>
       </c>
       <c r="V691" t="s">
-        <v>1689</v>
+        <v>1823</v>
       </c>
       <c r="W691" t="s">
         <v>988</v>
@@ -31104,7 +31506,7 @@
         <v>91</v>
       </c>
       <c r="V692" t="s">
-        <v>1690</v>
+        <v>1824</v>
       </c>
       <c r="W692" t="s">
         <v>985</v>
@@ -31118,7 +31520,7 @@
         <v>91</v>
       </c>
       <c r="V693" t="s">
-        <v>1691</v>
+        <v>1825</v>
       </c>
       <c r="W693" t="s">
         <v>985</v>
@@ -31132,7 +31534,7 @@
         <v>91</v>
       </c>
       <c r="V694" t="s">
-        <v>1692</v>
+        <v>1826</v>
       </c>
       <c r="W694" t="s">
         <v>979</v>
@@ -31146,7 +31548,7 @@
         <v>91</v>
       </c>
       <c r="V695" t="s">
-        <v>1693</v>
+        <v>1827</v>
       </c>
       <c r="W695" t="s">
         <v>979</v>
@@ -31160,7 +31562,7 @@
         <v>91</v>
       </c>
       <c r="V696" t="s">
-        <v>1694</v>
+        <v>1828</v>
       </c>
       <c r="W696" t="s">
         <v>1021</v>
@@ -31174,7 +31576,7 @@
         <v>91</v>
       </c>
       <c r="V697" t="s">
-        <v>1695</v>
+        <v>1829</v>
       </c>
       <c r="W697" t="s">
         <v>1021</v>
@@ -31188,7 +31590,7 @@
         <v>91</v>
       </c>
       <c r="V698" t="s">
-        <v>1696</v>
+        <v>1830</v>
       </c>
       <c r="W698" t="s">
         <v>1035</v>
@@ -31202,7 +31604,7 @@
         <v>91</v>
       </c>
       <c r="V699" t="s">
-        <v>1697</v>
+        <v>1831</v>
       </c>
       <c r="W699" t="s">
         <v>1035</v>
@@ -31216,10 +31618,10 @@
         <v>91</v>
       </c>
       <c r="V700" t="s">
-        <v>1698</v>
+        <v>1832</v>
       </c>
       <c r="W700" t="s">
-        <v>1586</v>
+        <v>1680</v>
       </c>
       <c r="X700" t="s">
         <v>1067</v>
@@ -31230,10 +31632,10 @@
         <v>91</v>
       </c>
       <c r="V701" t="s">
-        <v>1699</v>
+        <v>1833</v>
       </c>
       <c r="W701" t="s">
-        <v>1586</v>
+        <v>1680</v>
       </c>
       <c r="X701" t="s">
         <v>1067</v>
@@ -31244,7 +31646,7 @@
         <v>91</v>
       </c>
       <c r="V702" t="s">
-        <v>1700</v>
+        <v>1834</v>
       </c>
       <c r="W702" t="s">
         <v>1512</v>
@@ -31258,7 +31660,7 @@
         <v>91</v>
       </c>
       <c r="V703" t="s">
-        <v>1701</v>
+        <v>1835</v>
       </c>
       <c r="W703" t="s">
         <v>1512</v>
@@ -31272,10 +31674,10 @@
         <v>91</v>
       </c>
       <c r="V704" t="s">
-        <v>1702</v>
+        <v>1836</v>
       </c>
       <c r="W704" t="s">
-        <v>1703</v>
+        <v>1837</v>
       </c>
       <c r="X704" t="s">
         <v>1067</v>
@@ -31286,10 +31688,10 @@
         <v>91</v>
       </c>
       <c r="V705" t="s">
-        <v>1704</v>
+        <v>1838</v>
       </c>
       <c r="W705" t="s">
-        <v>1703</v>
+        <v>1837</v>
       </c>
       <c r="X705" t="s">
         <v>1067</v>
@@ -31300,10 +31702,10 @@
         <v>91</v>
       </c>
       <c r="V706" t="s">
-        <v>1705</v>
+        <v>1839</v>
       </c>
       <c r="W706" t="s">
-        <v>1588</v>
+        <v>1684</v>
       </c>
       <c r="X706" t="s">
         <v>1067</v>
@@ -31314,10 +31716,10 @@
         <v>91</v>
       </c>
       <c r="V707" t="s">
-        <v>1706</v>
+        <v>1840</v>
       </c>
       <c r="W707" t="s">
-        <v>1588</v>
+        <v>1684</v>
       </c>
       <c r="X707" t="s">
         <v>1067</v>
@@ -31328,10 +31730,10 @@
         <v>91</v>
       </c>
       <c r="V708" t="s">
-        <v>1707</v>
+        <v>1841</v>
       </c>
       <c r="W708" t="s">
-        <v>1708</v>
+        <v>1842</v>
       </c>
       <c r="X708" t="s">
         <v>1067</v>
@@ -31342,10 +31744,10 @@
         <v>91</v>
       </c>
       <c r="V709" t="s">
-        <v>1709</v>
+        <v>1843</v>
       </c>
       <c r="W709" t="s">
-        <v>1708</v>
+        <v>1842</v>
       </c>
       <c r="X709" t="s">
         <v>1067</v>
@@ -31356,10 +31758,10 @@
         <v>91</v>
       </c>
       <c r="V710" t="s">
-        <v>1710</v>
+        <v>1844</v>
       </c>
       <c r="W710" t="s">
-        <v>1711</v>
+        <v>1845</v>
       </c>
       <c r="X710" t="s">
         <v>1067</v>
@@ -31370,10 +31772,10 @@
         <v>91</v>
       </c>
       <c r="V711" t="s">
-        <v>1712</v>
+        <v>1846</v>
       </c>
       <c r="W711" t="s">
-        <v>1711</v>
+        <v>1845</v>
       </c>
       <c r="X711" t="s">
         <v>1067</v>
@@ -31384,10 +31786,10 @@
         <v>91</v>
       </c>
       <c r="V712" t="s">
-        <v>1713</v>
+        <v>1847</v>
       </c>
       <c r="W712" t="s">
-        <v>1714</v>
+        <v>1848</v>
       </c>
       <c r="X712" t="s">
         <v>1067</v>
@@ -31398,10 +31800,10 @@
         <v>91</v>
       </c>
       <c r="V713" t="s">
-        <v>1715</v>
+        <v>1849</v>
       </c>
       <c r="W713" t="s">
-        <v>1714</v>
+        <v>1848</v>
       </c>
       <c r="X713" t="s">
         <v>1067</v>
@@ -31412,10 +31814,10 @@
         <v>91</v>
       </c>
       <c r="V714" t="s">
-        <v>1716</v>
+        <v>1850</v>
       </c>
       <c r="W714" t="s">
-        <v>1717</v>
+        <v>1851</v>
       </c>
       <c r="X714" t="s">
         <v>1067</v>
@@ -31426,10 +31828,10 @@
         <v>91</v>
       </c>
       <c r="V715" t="s">
-        <v>1718</v>
+        <v>1852</v>
       </c>
       <c r="W715" t="s">
-        <v>1717</v>
+        <v>1851</v>
       </c>
       <c r="X715" t="s">
         <v>1067</v>
@@ -31440,7 +31842,7 @@
         <v>91</v>
       </c>
       <c r="V716" t="s">
-        <v>1719</v>
+        <v>1853</v>
       </c>
       <c r="W716" t="s">
         <v>990</v>
@@ -31454,7 +31856,7 @@
         <v>91</v>
       </c>
       <c r="V717" t="s">
-        <v>1720</v>
+        <v>1854</v>
       </c>
       <c r="W717" t="s">
         <v>990</v>
@@ -31468,10 +31870,10 @@
         <v>91</v>
       </c>
       <c r="V718" t="s">
-        <v>1721</v>
+        <v>1855</v>
       </c>
       <c r="W718" t="s">
-        <v>1524</v>
+        <v>1540</v>
       </c>
       <c r="X718" t="s">
         <v>1067</v>
@@ -31482,10 +31884,10 @@
         <v>91</v>
       </c>
       <c r="V719" t="s">
-        <v>1722</v>
+        <v>1856</v>
       </c>
       <c r="W719" t="s">
-        <v>1524</v>
+        <v>1540</v>
       </c>
       <c r="X719" t="s">
         <v>1067</v>
@@ -31496,10 +31898,10 @@
         <v>91</v>
       </c>
       <c r="V720" t="s">
-        <v>1723</v>
+        <v>1857</v>
       </c>
       <c r="W720" t="s">
-        <v>1724</v>
+        <v>1858</v>
       </c>
       <c r="X720" t="s">
         <v>1067</v>
@@ -31510,10 +31912,10 @@
         <v>91</v>
       </c>
       <c r="V721" t="s">
-        <v>1725</v>
+        <v>1859</v>
       </c>
       <c r="W721" t="s">
-        <v>1724</v>
+        <v>1858</v>
       </c>
       <c r="X721" t="s">
         <v>1067</v>
@@ -31524,10 +31926,10 @@
         <v>91</v>
       </c>
       <c r="V722" t="s">
-        <v>1726</v>
+        <v>1860</v>
       </c>
       <c r="W722" t="s">
-        <v>1727</v>
+        <v>1861</v>
       </c>
       <c r="X722" t="s">
         <v>1067</v>
@@ -31538,10 +31940,10 @@
         <v>91</v>
       </c>
       <c r="V723" t="s">
-        <v>1728</v>
+        <v>1862</v>
       </c>
       <c r="W723" t="s">
-        <v>1727</v>
+        <v>1861</v>
       </c>
       <c r="X723" t="s">
         <v>1067</v>
@@ -31552,7 +31954,7 @@
         <v>91</v>
       </c>
       <c r="V724" t="s">
-        <v>1729</v>
+        <v>1863</v>
       </c>
       <c r="W724" t="s">
         <v>993</v>
@@ -31566,7 +31968,7 @@
         <v>91</v>
       </c>
       <c r="V725" t="s">
-        <v>1730</v>
+        <v>1864</v>
       </c>
       <c r="W725" t="s">
         <v>993</v>
@@ -31580,7 +31982,7 @@
         <v>91</v>
       </c>
       <c r="V726" t="s">
-        <v>1731</v>
+        <v>1865</v>
       </c>
       <c r="W726" t="s">
         <v>975</v>
@@ -31594,7 +31996,7 @@
         <v>91</v>
       </c>
       <c r="V727" t="s">
-        <v>1732</v>
+        <v>1866</v>
       </c>
       <c r="W727" t="s">
         <v>975</v>
@@ -31608,10 +32010,10 @@
         <v>91</v>
       </c>
       <c r="V728" t="s">
-        <v>1733</v>
+        <v>1867</v>
       </c>
       <c r="W728" t="s">
-        <v>1734</v>
+        <v>1868</v>
       </c>
       <c r="X728" t="s">
         <v>1067</v>
@@ -31622,10 +32024,10 @@
         <v>91</v>
       </c>
       <c r="V729" t="s">
-        <v>1735</v>
+        <v>1869</v>
       </c>
       <c r="W729" t="s">
-        <v>1734</v>
+        <v>1868</v>
       </c>
       <c r="X729" t="s">
         <v>1067</v>
@@ -31636,10 +32038,10 @@
         <v>91</v>
       </c>
       <c r="V730" t="s">
-        <v>1736</v>
+        <v>1870</v>
       </c>
       <c r="W730" t="s">
-        <v>1737</v>
+        <v>1871</v>
       </c>
       <c r="X730" t="s">
         <v>1067</v>
@@ -31650,10 +32052,10 @@
         <v>91</v>
       </c>
       <c r="V731" t="s">
-        <v>1738</v>
+        <v>1872</v>
       </c>
       <c r="W731" t="s">
-        <v>1737</v>
+        <v>1871</v>
       </c>
       <c r="X731" t="s">
         <v>1067</v>
@@ -31664,7 +32066,7 @@
         <v>91</v>
       </c>
       <c r="V732" t="s">
-        <v>1739</v>
+        <v>1873</v>
       </c>
       <c r="W732" t="s">
         <v>1037</v>
@@ -31678,7 +32080,7 @@
         <v>91</v>
       </c>
       <c r="V733" t="s">
-        <v>1740</v>
+        <v>1874</v>
       </c>
       <c r="W733" t="s">
         <v>1037</v>
@@ -31692,7 +32094,7 @@
         <v>91</v>
       </c>
       <c r="V734" t="s">
-        <v>1741</v>
+        <v>1875</v>
       </c>
       <c r="W734" t="s">
         <v>998</v>
@@ -31706,7 +32108,7 @@
         <v>91</v>
       </c>
       <c r="V735" t="s">
-        <v>1742</v>
+        <v>1876</v>
       </c>
       <c r="W735" t="s">
         <v>998</v>
@@ -31720,7 +32122,7 @@
         <v>91</v>
       </c>
       <c r="V736" t="s">
-        <v>1743</v>
+        <v>1877</v>
       </c>
       <c r="W736" t="s">
         <v>1052</v>
@@ -31734,7 +32136,7 @@
         <v>91</v>
       </c>
       <c r="V737" t="s">
-        <v>1744</v>
+        <v>1878</v>
       </c>
       <c r="W737" t="s">
         <v>1052</v>
@@ -31748,7 +32150,7 @@
         <v>91</v>
       </c>
       <c r="V738" t="s">
-        <v>1745</v>
+        <v>1879</v>
       </c>
       <c r="W738" t="s">
         <v>1094</v>
@@ -31762,7 +32164,7 @@
         <v>91</v>
       </c>
       <c r="V739" t="s">
-        <v>1746</v>
+        <v>1880</v>
       </c>
       <c r="W739" t="s">
         <v>1094</v>
@@ -31776,7 +32178,7 @@
         <v>91</v>
       </c>
       <c r="V740" t="s">
-        <v>1747</v>
+        <v>1881</v>
       </c>
       <c r="W740" t="s">
         <v>1296</v>
@@ -31790,7 +32192,7 @@
         <v>91</v>
       </c>
       <c r="V741" t="s">
-        <v>1748</v>
+        <v>1882</v>
       </c>
       <c r="W741" t="s">
         <v>1296</v>
@@ -31804,7 +32206,7 @@
         <v>91</v>
       </c>
       <c r="V742" t="s">
-        <v>1749</v>
+        <v>1883</v>
       </c>
       <c r="W742" t="s">
         <v>1003</v>
@@ -31818,7 +32220,7 @@
         <v>91</v>
       </c>
       <c r="V743" t="s">
-        <v>1750</v>
+        <v>1884</v>
       </c>
       <c r="W743" t="s">
         <v>1003</v>
@@ -31832,7 +32234,7 @@
         <v>91</v>
       </c>
       <c r="V744" t="s">
-        <v>1751</v>
+        <v>1885</v>
       </c>
       <c r="W744" t="s">
         <v>1121</v>
@@ -31846,7 +32248,7 @@
         <v>91</v>
       </c>
       <c r="V745" t="s">
-        <v>1752</v>
+        <v>1886</v>
       </c>
       <c r="W745" t="s">
         <v>1121</v>
@@ -31860,7 +32262,7 @@
         <v>91</v>
       </c>
       <c r="V746" t="s">
-        <v>1753</v>
+        <v>1887</v>
       </c>
       <c r="W746" t="s">
         <v>1135</v>
@@ -31874,7 +32276,7 @@
         <v>91</v>
       </c>
       <c r="V747" t="s">
-        <v>1754</v>
+        <v>1888</v>
       </c>
       <c r="W747" t="s">
         <v>1135</v>
@@ -31888,7 +32290,7 @@
         <v>91</v>
       </c>
       <c r="V748" t="s">
-        <v>1755</v>
+        <v>1889</v>
       </c>
       <c r="W748" t="s">
         <v>1018</v>
@@ -31902,7 +32304,7 @@
         <v>91</v>
       </c>
       <c r="V749" t="s">
-        <v>1756</v>
+        <v>1890</v>
       </c>
       <c r="W749" t="s">
         <v>1018</v>
@@ -31916,7 +32318,7 @@
         <v>91</v>
       </c>
       <c r="V750" t="s">
-        <v>1757</v>
+        <v>1891</v>
       </c>
       <c r="W750" t="s">
         <v>1000</v>
@@ -31930,7 +32332,7 @@
         <v>91</v>
       </c>
       <c r="V751" t="s">
-        <v>1758</v>
+        <v>1892</v>
       </c>
       <c r="W751" t="s">
         <v>1000</v>
@@ -31944,10 +32346,10 @@
         <v>91</v>
       </c>
       <c r="V752" t="s">
-        <v>1759</v>
+        <v>1893</v>
       </c>
       <c r="W752" t="s">
-        <v>1760</v>
+        <v>1894</v>
       </c>
       <c r="X752" t="s">
         <v>1067</v>
@@ -31958,10 +32360,10 @@
         <v>91</v>
       </c>
       <c r="V753" t="s">
-        <v>1761</v>
+        <v>1895</v>
       </c>
       <c r="W753" t="s">
-        <v>1760</v>
+        <v>1894</v>
       </c>
       <c r="X753" t="s">
         <v>1067</v>
@@ -31972,7 +32374,7 @@
         <v>91</v>
       </c>
       <c r="V754" t="s">
-        <v>1762</v>
+        <v>1896</v>
       </c>
       <c r="W754" t="s">
         <v>1189</v>
@@ -31986,7 +32388,7 @@
         <v>91</v>
       </c>
       <c r="V755" t="s">
-        <v>1763</v>
+        <v>1897</v>
       </c>
       <c r="W755" t="s">
         <v>1189</v>
@@ -32000,7 +32402,7 @@
         <v>91</v>
       </c>
       <c r="V756" t="s">
-        <v>1764</v>
+        <v>1898</v>
       </c>
       <c r="W756" t="s">
         <v>1057</v>
@@ -32014,7 +32416,7 @@
         <v>91</v>
       </c>
       <c r="V757" t="s">
-        <v>1765</v>
+        <v>1899</v>
       </c>
       <c r="W757" t="s">
         <v>1057</v>
@@ -32028,7 +32430,7 @@
         <v>91</v>
       </c>
       <c r="V758" t="s">
-        <v>1766</v>
+        <v>1900</v>
       </c>
       <c r="W758" t="s">
         <v>983</v>
@@ -32042,7 +32444,7 @@
         <v>91</v>
       </c>
       <c r="V759" t="s">
-        <v>1767</v>
+        <v>1901</v>
       </c>
       <c r="W759" t="s">
         <v>983</v>
@@ -32056,7 +32458,7 @@
         <v>91</v>
       </c>
       <c r="V760" t="s">
-        <v>1768</v>
+        <v>1902</v>
       </c>
       <c r="W760" t="s">
         <v>970</v>
@@ -32070,7 +32472,7 @@
         <v>91</v>
       </c>
       <c r="V761" t="s">
-        <v>1769</v>
+        <v>1903</v>
       </c>
       <c r="W761" t="s">
         <v>970</v>
@@ -32084,7 +32486,7 @@
         <v>91</v>
       </c>
       <c r="V762" t="s">
-        <v>1770</v>
+        <v>1904</v>
       </c>
       <c r="W762" t="s">
         <v>1430</v>
@@ -32098,7 +32500,7 @@
         <v>91</v>
       </c>
       <c r="V763" t="s">
-        <v>1771</v>
+        <v>1905</v>
       </c>
       <c r="W763" t="s">
         <v>1430</v>
@@ -32112,7 +32514,7 @@
         <v>91</v>
       </c>
       <c r="V764" t="s">
-        <v>1772</v>
+        <v>1906</v>
       </c>
       <c r="W764" t="s">
         <v>986</v>
@@ -32126,7 +32528,7 @@
         <v>91</v>
       </c>
       <c r="V765" t="s">
-        <v>1773</v>
+        <v>1907</v>
       </c>
       <c r="W765" t="s">
         <v>986</v>
@@ -32140,7 +32542,7 @@
         <v>91</v>
       </c>
       <c r="V766" t="s">
-        <v>1774</v>
+        <v>1908</v>
       </c>
       <c r="W766" t="s">
         <v>1012</v>
@@ -32154,7 +32556,7 @@
         <v>91</v>
       </c>
       <c r="V767" t="s">
-        <v>1775</v>
+        <v>1909</v>
       </c>
       <c r="W767" t="s">
         <v>1012</v>
@@ -32168,7 +32570,7 @@
         <v>91</v>
       </c>
       <c r="V768" t="s">
-        <v>1776</v>
+        <v>1910</v>
       </c>
       <c r="W768" t="s">
         <v>1255</v>
@@ -32182,7 +32584,7 @@
         <v>91</v>
       </c>
       <c r="V769" t="s">
-        <v>1777</v>
+        <v>1911</v>
       </c>
       <c r="W769" t="s">
         <v>1255</v>
@@ -32196,7 +32598,7 @@
         <v>91</v>
       </c>
       <c r="V770" t="s">
-        <v>1778</v>
+        <v>1912</v>
       </c>
       <c r="W770" t="s">
         <v>987</v>
@@ -32210,7 +32612,7 @@
         <v>91</v>
       </c>
       <c r="V771" t="s">
-        <v>1779</v>
+        <v>1913</v>
       </c>
       <c r="W771" t="s">
         <v>987</v>
@@ -32224,7 +32626,7 @@
         <v>91</v>
       </c>
       <c r="V772" t="s">
-        <v>1780</v>
+        <v>1914</v>
       </c>
       <c r="W772" t="s">
         <v>1282</v>
@@ -32238,7 +32640,7 @@
         <v>91</v>
       </c>
       <c r="V773" t="s">
-        <v>1781</v>
+        <v>1915</v>
       </c>
       <c r="W773" t="s">
         <v>1282</v>
@@ -32252,7 +32654,7 @@
         <v>91</v>
       </c>
       <c r="V774" t="s">
-        <v>1782</v>
+        <v>1916</v>
       </c>
       <c r="W774" t="s">
         <v>1310</v>
@@ -32266,7 +32668,7 @@
         <v>91</v>
       </c>
       <c r="V775" t="s">
-        <v>1783</v>
+        <v>1917</v>
       </c>
       <c r="W775" t="s">
         <v>1310</v>
@@ -32280,7 +32682,7 @@
         <v>91</v>
       </c>
       <c r="V776" t="s">
-        <v>1784</v>
+        <v>1918</v>
       </c>
       <c r="W776" t="s">
         <v>1005</v>
@@ -32294,7 +32696,7 @@
         <v>91</v>
       </c>
       <c r="V777" t="s">
-        <v>1785</v>
+        <v>1919</v>
       </c>
       <c r="W777" t="s">
         <v>1005</v>
@@ -32308,7 +32710,7 @@
         <v>91</v>
       </c>
       <c r="V778" t="s">
-        <v>1786</v>
+        <v>1920</v>
       </c>
       <c r="W778" t="s">
         <v>1061</v>
@@ -32322,7 +32724,7 @@
         <v>91</v>
       </c>
       <c r="V779" t="s">
-        <v>1787</v>
+        <v>1921</v>
       </c>
       <c r="W779" t="s">
         <v>1061</v>
@@ -32336,7 +32738,7 @@
         <v>91</v>
       </c>
       <c r="V780" t="s">
-        <v>1788</v>
+        <v>1922</v>
       </c>
       <c r="W780" t="s">
         <v>997</v>
@@ -32350,7 +32752,7 @@
         <v>91</v>
       </c>
       <c r="V781" t="s">
-        <v>1789</v>
+        <v>1923</v>
       </c>
       <c r="W781" t="s">
         <v>997</v>
@@ -32364,7 +32766,7 @@
         <v>91</v>
       </c>
       <c r="V782" t="s">
-        <v>1790</v>
+        <v>1924</v>
       </c>
       <c r="W782" t="s">
         <v>1013</v>
@@ -32378,7 +32780,7 @@
         <v>91</v>
       </c>
       <c r="V783" t="s">
-        <v>1791</v>
+        <v>1925</v>
       </c>
       <c r="W783" t="s">
         <v>1013</v>
@@ -32392,7 +32794,7 @@
         <v>91</v>
       </c>
       <c r="V784" t="s">
-        <v>1792</v>
+        <v>1926</v>
       </c>
       <c r="W784" t="s">
         <v>1007</v>
@@ -32406,7 +32808,7 @@
         <v>91</v>
       </c>
       <c r="V785" t="s">
-        <v>1793</v>
+        <v>1927</v>
       </c>
       <c r="W785" t="s">
         <v>1007</v>
@@ -32420,7 +32822,7 @@
         <v>91</v>
       </c>
       <c r="V786" t="s">
-        <v>1794</v>
+        <v>1928</v>
       </c>
       <c r="W786" t="s">
         <v>1053</v>
@@ -32434,7 +32836,7 @@
         <v>91</v>
       </c>
       <c r="V787" t="s">
-        <v>1795</v>
+        <v>1929</v>
       </c>
       <c r="W787" t="s">
         <v>1053</v>
@@ -32448,7 +32850,7 @@
         <v>91</v>
       </c>
       <c r="V788" t="s">
-        <v>1796</v>
+        <v>1930</v>
       </c>
       <c r="W788" t="s">
         <v>995</v>
@@ -32462,7 +32864,7 @@
         <v>91</v>
       </c>
       <c r="V789" t="s">
-        <v>1797</v>
+        <v>1931</v>
       </c>
       <c r="W789" t="s">
         <v>995</v>
@@ -32476,7 +32878,7 @@
         <v>91</v>
       </c>
       <c r="V790" t="s">
-        <v>1798</v>
+        <v>1932</v>
       </c>
       <c r="W790" t="s">
         <v>1029</v>
@@ -32490,7 +32892,7 @@
         <v>91</v>
       </c>
       <c r="V791" t="s">
-        <v>1799</v>
+        <v>1933</v>
       </c>
       <c r="W791" t="s">
         <v>1029</v>
@@ -32504,10 +32906,10 @@
         <v>91</v>
       </c>
       <c r="V792" t="s">
-        <v>1800</v>
+        <v>1934</v>
       </c>
       <c r="W792" t="s">
-        <v>1801</v>
+        <v>1935</v>
       </c>
       <c r="X792" t="s">
         <v>1067</v>
@@ -32518,10 +32920,10 @@
         <v>91</v>
       </c>
       <c r="V793" t="s">
-        <v>1802</v>
+        <v>1936</v>
       </c>
       <c r="W793" t="s">
-        <v>1801</v>
+        <v>1935</v>
       </c>
       <c r="X793" t="s">
         <v>1067</v>
@@ -32532,7 +32934,7 @@
         <v>91</v>
       </c>
       <c r="V794" t="s">
-        <v>1803</v>
+        <v>1937</v>
       </c>
       <c r="W794" t="s">
         <v>1402</v>
@@ -32546,7 +32948,7 @@
         <v>91</v>
       </c>
       <c r="V795" t="s">
-        <v>1804</v>
+        <v>1938</v>
       </c>
       <c r="W795" t="s">
         <v>1402</v>
@@ -32560,7 +32962,7 @@
         <v>91</v>
       </c>
       <c r="V796" t="s">
-        <v>1805</v>
+        <v>1939</v>
       </c>
       <c r="W796" t="s">
         <v>1416</v>
@@ -32574,7 +32976,7 @@
         <v>91</v>
       </c>
       <c r="V797" t="s">
-        <v>1806</v>
+        <v>1940</v>
       </c>
       <c r="W797" t="s">
         <v>1416</v>
@@ -32588,10 +32990,10 @@
         <v>91</v>
       </c>
       <c r="V798" t="s">
-        <v>1807</v>
+        <v>1941</v>
       </c>
       <c r="W798" t="s">
-        <v>1808</v>
+        <v>1942</v>
       </c>
       <c r="X798" t="s">
         <v>1067</v>
@@ -32602,10 +33004,10 @@
         <v>91</v>
       </c>
       <c r="V799" t="s">
-        <v>1809</v>
+        <v>1943</v>
       </c>
       <c r="W799" t="s">
-        <v>1808</v>
+        <v>1942</v>
       </c>
       <c r="X799" t="s">
         <v>1067</v>
@@ -32616,7 +33018,7 @@
         <v>91</v>
       </c>
       <c r="V800" t="s">
-        <v>1810</v>
+        <v>1944</v>
       </c>
       <c r="W800" t="s">
         <v>1444</v>
@@ -32630,7 +33032,7 @@
         <v>91</v>
       </c>
       <c r="V801" t="s">
-        <v>1811</v>
+        <v>1945</v>
       </c>
       <c r="W801" t="s">
         <v>1444</v>
@@ -32644,7 +33046,7 @@
         <v>91</v>
       </c>
       <c r="V802" t="s">
-        <v>1812</v>
+        <v>1946</v>
       </c>
       <c r="W802" t="s">
         <v>1058</v>
@@ -32658,7 +33060,7 @@
         <v>91</v>
       </c>
       <c r="V803" t="s">
-        <v>1813</v>
+        <v>1947</v>
       </c>
       <c r="W803" t="s">
         <v>1058</v>
@@ -32672,7 +33074,7 @@
         <v>91</v>
       </c>
       <c r="V804" t="s">
-        <v>1814</v>
+        <v>1948</v>
       </c>
       <c r="W804" t="s">
         <v>1030</v>
@@ -32686,7 +33088,7 @@
         <v>91</v>
       </c>
       <c r="V805" t="s">
-        <v>1815</v>
+        <v>1949</v>
       </c>
       <c r="W805" t="s">
         <v>1030</v>
@@ -32700,7 +33102,7 @@
         <v>91</v>
       </c>
       <c r="V806" t="s">
-        <v>1816</v>
+        <v>1950</v>
       </c>
       <c r="W806" t="s">
         <v>1484</v>
@@ -32714,7 +33116,7 @@
         <v>91</v>
       </c>
       <c r="V807" t="s">
-        <v>1817</v>
+        <v>1951</v>
       </c>
       <c r="W807" t="s">
         <v>1484</v>
@@ -32728,7 +33130,7 @@
         <v>91</v>
       </c>
       <c r="V808" t="s">
-        <v>1818</v>
+        <v>1952</v>
       </c>
       <c r="W808" t="s">
         <v>1498</v>
@@ -32742,7 +33144,7 @@
         <v>91</v>
       </c>
       <c r="V809" t="s">
-        <v>1819</v>
+        <v>1953</v>
       </c>
       <c r="W809" t="s">
         <v>1498</v>
@@ -32756,10 +33158,10 @@
         <v>91</v>
       </c>
       <c r="V810" t="s">
-        <v>1820</v>
+        <v>1954</v>
       </c>
       <c r="W810" t="s">
-        <v>1821</v>
+        <v>1955</v>
       </c>
       <c r="X810" t="s">
         <v>1067</v>
@@ -32770,10 +33172,10 @@
         <v>91</v>
       </c>
       <c r="V811" t="s">
-        <v>1822</v>
+        <v>1956</v>
       </c>
       <c r="W811" t="s">
-        <v>1821</v>
+        <v>1955</v>
       </c>
       <c r="X811" t="s">
         <v>1067</v>
@@ -32784,10 +33186,10 @@
         <v>91</v>
       </c>
       <c r="V812" t="s">
-        <v>1823</v>
+        <v>1957</v>
       </c>
       <c r="W812" t="s">
-        <v>1824</v>
+        <v>1958</v>
       </c>
       <c r="X812" t="s">
         <v>1067</v>
@@ -32798,10 +33200,10 @@
         <v>91</v>
       </c>
       <c r="V813" t="s">
-        <v>1825</v>
+        <v>1959</v>
       </c>
       <c r="W813" t="s">
-        <v>1824</v>
+        <v>1958</v>
       </c>
       <c r="X813" t="s">
         <v>1067</v>
@@ -32812,10 +33214,10 @@
         <v>91</v>
       </c>
       <c r="V814" t="s">
-        <v>1826</v>
+        <v>1960</v>
       </c>
       <c r="W814" t="s">
-        <v>1827</v>
+        <v>1961</v>
       </c>
       <c r="X814" t="s">
         <v>1067</v>
@@ -32826,10 +33228,10 @@
         <v>91</v>
       </c>
       <c r="V815" t="s">
-        <v>1828</v>
+        <v>1962</v>
       </c>
       <c r="W815" t="s">
-        <v>1827</v>
+        <v>1961</v>
       </c>
       <c r="X815" t="s">
         <v>1067</v>
@@ -32840,10 +33242,10 @@
         <v>91</v>
       </c>
       <c r="V816" t="s">
-        <v>1829</v>
+        <v>1963</v>
       </c>
       <c r="W816" t="s">
-        <v>1830</v>
+        <v>1964</v>
       </c>
       <c r="X816" t="s">
         <v>1067</v>
@@ -32854,10 +33256,10 @@
         <v>91</v>
       </c>
       <c r="V817" t="s">
-        <v>1831</v>
+        <v>1965</v>
       </c>
       <c r="W817" t="s">
-        <v>1830</v>
+        <v>1964</v>
       </c>
       <c r="X817" t="s">
         <v>1067</v>
@@ -32868,7 +33270,7 @@
         <v>91</v>
       </c>
       <c r="V818" t="s">
-        <v>1832</v>
+        <v>1966</v>
       </c>
       <c r="W818" t="s">
         <v>1047</v>
@@ -32882,7 +33284,7 @@
         <v>91</v>
       </c>
       <c r="V819" t="s">
-        <v>1833</v>
+        <v>1967</v>
       </c>
       <c r="W819" t="s">
         <v>1047</v>
@@ -32896,10 +33298,10 @@
         <v>91</v>
       </c>
       <c r="V820" t="s">
-        <v>1834</v>
+        <v>1968</v>
       </c>
       <c r="W820" t="s">
-        <v>1835</v>
+        <v>1969</v>
       </c>
       <c r="X820" t="s">
         <v>1067</v>
@@ -32910,10 +33312,10 @@
         <v>91</v>
       </c>
       <c r="V821" t="s">
-        <v>1836</v>
+        <v>1970</v>
       </c>
       <c r="W821" t="s">
-        <v>1835</v>
+        <v>1969</v>
       </c>
       <c r="X821" t="s">
         <v>1067</v>
@@ -32924,7 +33326,7 @@
         <v>91</v>
       </c>
       <c r="V822" t="s">
-        <v>1837</v>
+        <v>1971</v>
       </c>
       <c r="W822" t="s">
         <v>1036</v>
@@ -32938,7 +33340,7 @@
         <v>91</v>
       </c>
       <c r="V823" t="s">
-        <v>1838</v>
+        <v>1972</v>
       </c>
       <c r="W823" t="s">
         <v>1036</v>
@@ -32952,7 +33354,7 @@
         <v>91</v>
       </c>
       <c r="V824" t="s">
-        <v>1839</v>
+        <v>1973</v>
       </c>
       <c r="W824" t="s">
         <v>1002</v>
@@ -32966,7 +33368,7 @@
         <v>91</v>
       </c>
       <c r="V825" t="s">
-        <v>1840</v>
+        <v>1974</v>
       </c>
       <c r="W825" t="s">
         <v>1002</v>
@@ -32980,10 +33382,10 @@
         <v>91</v>
       </c>
       <c r="V826" t="s">
-        <v>1841</v>
+        <v>1975</v>
       </c>
       <c r="W826" t="s">
-        <v>1516</v>
+        <v>1522</v>
       </c>
       <c r="X826" t="s">
         <v>1067</v>
@@ -32994,10 +33396,10 @@
         <v>91</v>
       </c>
       <c r="V827" t="s">
-        <v>1842</v>
+        <v>1976</v>
       </c>
       <c r="W827" t="s">
-        <v>1516</v>
+        <v>1522</v>
       </c>
       <c r="X827" t="s">
         <v>1067</v>
@@ -33008,7 +33410,7 @@
         <v>91</v>
       </c>
       <c r="V828" t="s">
-        <v>1843</v>
+        <v>1977</v>
       </c>
       <c r="W828" t="s">
         <v>1034</v>
@@ -33022,7 +33424,7 @@
         <v>91</v>
       </c>
       <c r="V829" t="s">
-        <v>1844</v>
+        <v>1978</v>
       </c>
       <c r="W829" t="s">
         <v>1034</v>
@@ -33036,10 +33438,10 @@
         <v>91</v>
       </c>
       <c r="V830" t="s">
-        <v>1845</v>
+        <v>1979</v>
       </c>
       <c r="W830" t="s">
-        <v>1519</v>
+        <v>1529</v>
       </c>
       <c r="X830" t="s">
         <v>1067</v>
@@ -33050,10 +33452,10 @@
         <v>91</v>
       </c>
       <c r="V831" t="s">
-        <v>1846</v>
+        <v>1980</v>
       </c>
       <c r="W831" t="s">
-        <v>1519</v>
+        <v>1529</v>
       </c>
       <c r="X831" t="s">
         <v>1067</v>
@@ -33064,10 +33466,10 @@
         <v>91</v>
       </c>
       <c r="V832" t="s">
-        <v>1847</v>
+        <v>1981</v>
       </c>
       <c r="W832" t="s">
-        <v>1526</v>
+        <v>1544</v>
       </c>
       <c r="X832" t="s">
         <v>1067</v>
@@ -33078,10 +33480,10 @@
         <v>91</v>
       </c>
       <c r="V833" t="s">
-        <v>1848</v>
+        <v>1982</v>
       </c>
       <c r="W833" t="s">
-        <v>1526</v>
+        <v>1544</v>
       </c>
       <c r="X833" t="s">
         <v>1067</v>
@@ -33092,10 +33494,10 @@
         <v>91</v>
       </c>
       <c r="V834" t="s">
-        <v>1849</v>
+        <v>1983</v>
       </c>
       <c r="W834" t="s">
-        <v>1528</v>
+        <v>1548</v>
       </c>
       <c r="X834" t="s">
         <v>1067</v>
@@ -33106,10 +33508,10 @@
         <v>91</v>
       </c>
       <c r="V835" t="s">
-        <v>1850</v>
+        <v>1984</v>
       </c>
       <c r="W835" t="s">
-        <v>1528</v>
+        <v>1548</v>
       </c>
       <c r="X835" t="s">
         <v>1067</v>
@@ -33120,10 +33522,10 @@
         <v>91</v>
       </c>
       <c r="V836" t="s">
-        <v>1851</v>
+        <v>1985</v>
       </c>
       <c r="W836" t="s">
-        <v>1530</v>
+        <v>1552</v>
       </c>
       <c r="X836" t="s">
         <v>1067</v>
@@ -33134,10 +33536,10 @@
         <v>91</v>
       </c>
       <c r="V837" t="s">
-        <v>1852</v>
+        <v>1986</v>
       </c>
       <c r="W837" t="s">
-        <v>1530</v>
+        <v>1552</v>
       </c>
       <c r="X837" t="s">
         <v>1067</v>
@@ -33148,10 +33550,10 @@
         <v>91</v>
       </c>
       <c r="V838" t="s">
-        <v>1853</v>
+        <v>1987</v>
       </c>
       <c r="W838" t="s">
-        <v>1534</v>
+        <v>1562</v>
       </c>
       <c r="X838" t="s">
         <v>1067</v>
@@ -33162,10 +33564,10 @@
         <v>91</v>
       </c>
       <c r="V839" t="s">
-        <v>1854</v>
+        <v>1988</v>
       </c>
       <c r="W839" t="s">
-        <v>1534</v>
+        <v>1562</v>
       </c>
       <c r="X839" t="s">
         <v>1067</v>
@@ -33176,10 +33578,10 @@
         <v>91</v>
       </c>
       <c r="V840" t="s">
-        <v>1855</v>
+        <v>1989</v>
       </c>
       <c r="W840" t="s">
-        <v>1536</v>
+        <v>1566</v>
       </c>
       <c r="X840" t="s">
         <v>1067</v>
@@ -33190,10 +33592,10 @@
         <v>91</v>
       </c>
       <c r="V841" t="s">
-        <v>1856</v>
+        <v>1990</v>
       </c>
       <c r="W841" t="s">
-        <v>1536</v>
+        <v>1566</v>
       </c>
       <c r="X841" t="s">
         <v>1067</v>
@@ -33204,10 +33606,10 @@
         <v>91</v>
       </c>
       <c r="V842" t="s">
-        <v>1857</v>
+        <v>1991</v>
       </c>
       <c r="W842" t="s">
-        <v>1539</v>
+        <v>1573</v>
       </c>
       <c r="X842" t="s">
         <v>1067</v>
@@ -33218,10 +33620,10 @@
         <v>91</v>
       </c>
       <c r="V843" t="s">
-        <v>1858</v>
+        <v>1992</v>
       </c>
       <c r="W843" t="s">
-        <v>1539</v>
+        <v>1573</v>
       </c>
       <c r="X843" t="s">
         <v>1067</v>
@@ -33232,10 +33634,10 @@
         <v>91</v>
       </c>
       <c r="V844" t="s">
-        <v>1859</v>
+        <v>1993</v>
       </c>
       <c r="W844" t="s">
-        <v>1541</v>
+        <v>1577</v>
       </c>
       <c r="X844" t="s">
         <v>1067</v>
@@ -33246,10 +33648,10 @@
         <v>91</v>
       </c>
       <c r="V845" t="s">
-        <v>1860</v>
+        <v>1994</v>
       </c>
       <c r="W845" t="s">
-        <v>1541</v>
+        <v>1577</v>
       </c>
       <c r="X845" t="s">
         <v>1067</v>
@@ -33260,7 +33662,7 @@
         <v>91</v>
       </c>
       <c r="V846" t="s">
-        <v>1861</v>
+        <v>1995</v>
       </c>
       <c r="W846" t="s">
         <v>1027</v>
@@ -33274,7 +33676,7 @@
         <v>91</v>
       </c>
       <c r="V847" t="s">
-        <v>1862</v>
+        <v>1996</v>
       </c>
       <c r="W847" t="s">
         <v>1027</v>
@@ -33288,10 +33690,10 @@
         <v>91</v>
       </c>
       <c r="V848" t="s">
-        <v>1863</v>
+        <v>1997</v>
       </c>
       <c r="W848" t="s">
-        <v>1544</v>
+        <v>1584</v>
       </c>
       <c r="X848" t="s">
         <v>1067</v>
@@ -33302,10 +33704,10 @@
         <v>91</v>
       </c>
       <c r="V849" t="s">
-        <v>1864</v>
+        <v>1998</v>
       </c>
       <c r="W849" t="s">
-        <v>1544</v>
+        <v>1584</v>
       </c>
       <c r="X849" t="s">
         <v>1067</v>
@@ -33316,7 +33718,7 @@
         <v>91</v>
       </c>
       <c r="V850" t="s">
-        <v>1865</v>
+        <v>1999</v>
       </c>
       <c r="W850" t="s">
         <v>974</v>
@@ -33330,7 +33732,7 @@
         <v>91</v>
       </c>
       <c r="V851" t="s">
-        <v>1866</v>
+        <v>2000</v>
       </c>
       <c r="W851" t="s">
         <v>974</v>
@@ -33344,7 +33746,7 @@
         <v>91</v>
       </c>
       <c r="V852" t="s">
-        <v>1867</v>
+        <v>2001</v>
       </c>
       <c r="W852" t="s">
         <v>1004</v>
@@ -33358,7 +33760,7 @@
         <v>91</v>
       </c>
       <c r="V853" t="s">
-        <v>1868</v>
+        <v>2002</v>
       </c>
       <c r="W853" t="s">
         <v>1004</v>
@@ -33372,10 +33774,10 @@
         <v>91</v>
       </c>
       <c r="V854" t="s">
-        <v>1869</v>
+        <v>2003</v>
       </c>
       <c r="W854" t="s">
-        <v>1549</v>
+        <v>1597</v>
       </c>
       <c r="X854" t="s">
         <v>1067</v>
@@ -33386,10 +33788,10 @@
         <v>91</v>
       </c>
       <c r="V855" t="s">
-        <v>1870</v>
+        <v>2004</v>
       </c>
       <c r="W855" t="s">
-        <v>1549</v>
+        <v>1597</v>
       </c>
       <c r="X855" t="s">
         <v>1067</v>
@@ -33400,10 +33802,10 @@
         <v>91</v>
       </c>
       <c r="V856" t="s">
-        <v>1871</v>
+        <v>2005</v>
       </c>
       <c r="W856" t="s">
-        <v>1551</v>
+        <v>1601</v>
       </c>
       <c r="X856" t="s">
         <v>1067</v>
@@ -33414,10 +33816,10 @@
         <v>91</v>
       </c>
       <c r="V857" t="s">
-        <v>1872</v>
+        <v>2006</v>
       </c>
       <c r="W857" t="s">
-        <v>1551</v>
+        <v>1601</v>
       </c>
       <c r="X857" t="s">
         <v>1067</v>
@@ -33428,10 +33830,10 @@
         <v>91</v>
       </c>
       <c r="V858" t="s">
-        <v>1873</v>
+        <v>2007</v>
       </c>
       <c r="W858" t="s">
-        <v>1554</v>
+        <v>1608</v>
       </c>
       <c r="X858" t="s">
         <v>1067</v>
@@ -33442,10 +33844,10 @@
         <v>91</v>
       </c>
       <c r="V859" t="s">
-        <v>1874</v>
+        <v>2008</v>
       </c>
       <c r="W859" t="s">
-        <v>1554</v>
+        <v>1608</v>
       </c>
       <c r="X859" t="s">
         <v>1067</v>
@@ -33456,10 +33858,10 @@
         <v>91</v>
       </c>
       <c r="V860" t="s">
-        <v>1875</v>
+        <v>2009</v>
       </c>
       <c r="W860" t="s">
-        <v>1556</v>
+        <v>1612</v>
       </c>
       <c r="X860" t="s">
         <v>1067</v>
@@ -33470,10 +33872,10 @@
         <v>91</v>
       </c>
       <c r="V861" t="s">
-        <v>1876</v>
+        <v>2010</v>
       </c>
       <c r="W861" t="s">
-        <v>1556</v>
+        <v>1612</v>
       </c>
       <c r="X861" t="s">
         <v>1067</v>
@@ -33484,10 +33886,10 @@
         <v>91</v>
       </c>
       <c r="V862" t="s">
-        <v>1877</v>
+        <v>2011</v>
       </c>
       <c r="W862" t="s">
-        <v>1558</v>
+        <v>1616</v>
       </c>
       <c r="X862" t="s">
         <v>1067</v>
@@ -33498,10 +33900,10 @@
         <v>91</v>
       </c>
       <c r="V863" t="s">
-        <v>1878</v>
+        <v>2012</v>
       </c>
       <c r="W863" t="s">
-        <v>1558</v>
+        <v>1616</v>
       </c>
       <c r="X863" t="s">
         <v>1067</v>
@@ -33512,10 +33914,10 @@
         <v>91</v>
       </c>
       <c r="V864" t="s">
-        <v>1879</v>
+        <v>2013</v>
       </c>
       <c r="W864" t="s">
-        <v>1564</v>
+        <v>1630</v>
       </c>
       <c r="X864" t="s">
         <v>1067</v>
@@ -33526,10 +33928,10 @@
         <v>91</v>
       </c>
       <c r="V865" t="s">
-        <v>1880</v>
+        <v>2014</v>
       </c>
       <c r="W865" t="s">
-        <v>1564</v>
+        <v>1630</v>
       </c>
       <c r="X865" t="s">
         <v>1067</v>
@@ -33540,10 +33942,10 @@
         <v>91</v>
       </c>
       <c r="V866" t="s">
-        <v>1881</v>
+        <v>2015</v>
       </c>
       <c r="W866" t="s">
-        <v>1567</v>
+        <v>1637</v>
       </c>
       <c r="X866" t="s">
         <v>1067</v>
@@ -33554,10 +33956,10 @@
         <v>91</v>
       </c>
       <c r="V867" t="s">
-        <v>1882</v>
+        <v>2016</v>
       </c>
       <c r="W867" t="s">
-        <v>1567</v>
+        <v>1637</v>
       </c>
       <c r="X867" t="s">
         <v>1067</v>
@@ -33568,10 +33970,10 @@
         <v>91</v>
       </c>
       <c r="V868" t="s">
-        <v>1883</v>
+        <v>2017</v>
       </c>
       <c r="W868" t="s">
-        <v>1569</v>
+        <v>1641</v>
       </c>
       <c r="X868" t="s">
         <v>1067</v>
@@ -33582,10 +33984,10 @@
         <v>91</v>
       </c>
       <c r="V869" t="s">
-        <v>1884</v>
+        <v>2018</v>
       </c>
       <c r="W869" t="s">
-        <v>1569</v>
+        <v>1641</v>
       </c>
       <c r="X869" t="s">
         <v>1067</v>
@@ -33596,7 +33998,7 @@
         <v>91</v>
       </c>
       <c r="V870" t="s">
-        <v>1885</v>
+        <v>2019</v>
       </c>
       <c r="W870" t="s">
         <v>1040</v>
@@ -33610,7 +34012,7 @@
         <v>91</v>
       </c>
       <c r="V871" t="s">
-        <v>1886</v>
+        <v>2020</v>
       </c>
       <c r="W871" t="s">
         <v>1040</v>
@@ -33624,7 +34026,7 @@
         <v>91</v>
       </c>
       <c r="V872" t="s">
-        <v>1887</v>
+        <v>2021</v>
       </c>
       <c r="W872" t="s">
         <v>1019</v>
@@ -33638,7 +34040,7 @@
         <v>91</v>
       </c>
       <c r="V873" t="s">
-        <v>1888</v>
+        <v>2022</v>
       </c>
       <c r="W873" t="s">
         <v>1019</v>
@@ -33652,10 +34054,10 @@
         <v>91</v>
       </c>
       <c r="V874" t="s">
-        <v>1889</v>
+        <v>2023</v>
       </c>
       <c r="W874" t="s">
-        <v>1574</v>
+        <v>1654</v>
       </c>
       <c r="X874" t="s">
         <v>1067</v>
@@ -33666,10 +34068,10 @@
         <v>91</v>
       </c>
       <c r="V875" t="s">
-        <v>1890</v>
+        <v>2024</v>
       </c>
       <c r="W875" t="s">
-        <v>1574</v>
+        <v>1654</v>
       </c>
       <c r="X875" t="s">
         <v>1067</v>
@@ -33680,10 +34082,10 @@
         <v>91</v>
       </c>
       <c r="V876" t="s">
-        <v>1891</v>
+        <v>2025</v>
       </c>
       <c r="W876" t="s">
-        <v>1577</v>
+        <v>1661</v>
       </c>
       <c r="X876" t="s">
         <v>1067</v>
@@ -33694,10 +34096,10 @@
         <v>91</v>
       </c>
       <c r="V877" t="s">
-        <v>1892</v>
+        <v>2026</v>
       </c>
       <c r="W877" t="s">
-        <v>1577</v>
+        <v>1661</v>
       </c>
       <c r="X877" t="s">
         <v>1067</v>
@@ -33708,10 +34110,10 @@
         <v>91</v>
       </c>
       <c r="V878" t="s">
-        <v>1893</v>
+        <v>2027</v>
       </c>
       <c r="W878" t="s">
-        <v>1579</v>
+        <v>1665</v>
       </c>
       <c r="X878" t="s">
         <v>1067</v>
@@ -33722,10 +34124,10 @@
         <v>91</v>
       </c>
       <c r="V879" t="s">
-        <v>1894</v>
+        <v>2028</v>
       </c>
       <c r="W879" t="s">
-        <v>1579</v>
+        <v>1665</v>
       </c>
       <c r="X879" t="s">
         <v>1067</v>
@@ -33736,10 +34138,10 @@
         <v>91</v>
       </c>
       <c r="V880" t="s">
-        <v>1895</v>
+        <v>2029</v>
       </c>
       <c r="W880" t="s">
-        <v>1581</v>
+        <v>1669</v>
       </c>
       <c r="X880" t="s">
         <v>1067</v>
@@ -33750,10 +34152,10 @@
         <v>91</v>
       </c>
       <c r="V881" t="s">
-        <v>1896</v>
+        <v>2030</v>
       </c>
       <c r="W881" t="s">
-        <v>1581</v>
+        <v>1669</v>
       </c>
       <c r="X881" t="s">
         <v>1067</v>
@@ -33764,7 +34166,7 @@
         <v>91</v>
       </c>
       <c r="V882" t="s">
-        <v>1897</v>
+        <v>2031</v>
       </c>
       <c r="W882" t="s">
         <v>1016</v>
@@ -33778,7 +34180,7 @@
         <v>91</v>
       </c>
       <c r="V883" t="s">
-        <v>1898</v>
+        <v>2032</v>
       </c>
       <c r="W883" t="s">
         <v>1016</v>
@@ -33792,10 +34194,10 @@
         <v>91</v>
       </c>
       <c r="V884" t="s">
-        <v>1899</v>
+        <v>2033</v>
       </c>
       <c r="W884" t="s">
-        <v>1591</v>
+        <v>1691</v>
       </c>
       <c r="X884" t="s">
         <v>1067</v>
@@ -33806,10 +34208,10 @@
         <v>91</v>
       </c>
       <c r="V885" t="s">
-        <v>1900</v>
+        <v>2034</v>
       </c>
       <c r="W885" t="s">
-        <v>1591</v>
+        <v>1691</v>
       </c>
       <c r="X885" t="s">
         <v>1067</v>
@@ -33820,10 +34222,10 @@
         <v>91</v>
       </c>
       <c r="V886" t="s">
-        <v>1901</v>
+        <v>2035</v>
       </c>
       <c r="W886" t="s">
-        <v>1594</v>
+        <v>1698</v>
       </c>
       <c r="X886" t="s">
         <v>1067</v>
@@ -33834,10 +34236,10 @@
         <v>91</v>
       </c>
       <c r="V887" t="s">
-        <v>1902</v>
+        <v>2036</v>
       </c>
       <c r="W887" t="s">
-        <v>1594</v>
+        <v>1698</v>
       </c>
       <c r="X887" t="s">
         <v>1067</v>
@@ -33848,10 +34250,10 @@
         <v>91</v>
       </c>
       <c r="V888" t="s">
-        <v>1903</v>
+        <v>2037</v>
       </c>
       <c r="W888" t="s">
-        <v>1596</v>
+        <v>1702</v>
       </c>
       <c r="X888" t="s">
         <v>1067</v>
@@ -33862,10 +34264,10 @@
         <v>91</v>
       </c>
       <c r="V889" t="s">
-        <v>1904</v>
+        <v>2038</v>
       </c>
       <c r="W889" t="s">
-        <v>1596</v>
+        <v>1702</v>
       </c>
       <c r="X889" t="s">
         <v>1067</v>
@@ -33876,10 +34278,10 @@
         <v>91</v>
       </c>
       <c r="V890" t="s">
-        <v>1905</v>
+        <v>2039</v>
       </c>
       <c r="W890" t="s">
-        <v>1598</v>
+        <v>1706</v>
       </c>
       <c r="X890" t="s">
         <v>1067</v>
@@ -33890,10 +34292,10 @@
         <v>91</v>
       </c>
       <c r="V891" t="s">
-        <v>1906</v>
+        <v>2040</v>
       </c>
       <c r="W891" t="s">
-        <v>1598</v>
+        <v>1706</v>
       </c>
       <c r="X891" t="s">
         <v>1067</v>
@@ -33904,7 +34306,7 @@
         <v>91</v>
       </c>
       <c r="V892" t="s">
-        <v>1907</v>
+        <v>2041</v>
       </c>
       <c r="W892" t="s">
         <v>1017</v>
@@ -33918,7 +34320,7 @@
         <v>91</v>
       </c>
       <c r="V893" t="s">
-        <v>1908</v>
+        <v>2042</v>
       </c>
       <c r="W893" t="s">
         <v>1017</v>
@@ -33932,10 +34334,10 @@
         <v>91</v>
       </c>
       <c r="V894" t="s">
-        <v>1909</v>
+        <v>2043</v>
       </c>
       <c r="W894" t="s">
-        <v>1601</v>
+        <v>1713</v>
       </c>
       <c r="X894" t="s">
         <v>1067</v>
@@ -33946,10 +34348,10 @@
         <v>91</v>
       </c>
       <c r="V895" t="s">
-        <v>1910</v>
+        <v>2044</v>
       </c>
       <c r="W895" t="s">
-        <v>1601</v>
+        <v>1713</v>
       </c>
       <c r="X895" t="s">
         <v>1067</v>
@@ -33960,10 +34362,10 @@
         <v>91</v>
       </c>
       <c r="V896" t="s">
-        <v>1911</v>
+        <v>2045</v>
       </c>
       <c r="W896" t="s">
-        <v>1603</v>
+        <v>1717</v>
       </c>
       <c r="X896" t="s">
         <v>1067</v>
@@ -33974,10 +34376,10 @@
         <v>91</v>
       </c>
       <c r="V897" t="s">
-        <v>1912</v>
+        <v>2046</v>
       </c>
       <c r="W897" t="s">
-        <v>1603</v>
+        <v>1717</v>
       </c>
       <c r="X897" t="s">
         <v>1067</v>
@@ -33988,10 +34390,10 @@
         <v>91</v>
       </c>
       <c r="V898" t="s">
-        <v>1913</v>
+        <v>2047</v>
       </c>
       <c r="W898" t="s">
-        <v>1605</v>
+        <v>1721</v>
       </c>
       <c r="X898" t="s">
         <v>1067</v>
@@ -34002,10 +34404,10 @@
         <v>91</v>
       </c>
       <c r="V899" t="s">
-        <v>1914</v>
+        <v>2048</v>
       </c>
       <c r="W899" t="s">
-        <v>1605</v>
+        <v>1721</v>
       </c>
       <c r="X899" t="s">
         <v>1067</v>
@@ -34016,10 +34418,10 @@
         <v>91</v>
       </c>
       <c r="V900" t="s">
-        <v>1915</v>
+        <v>2049</v>
       </c>
       <c r="W900" t="s">
-        <v>1607</v>
+        <v>1725</v>
       </c>
       <c r="X900" t="s">
         <v>1067</v>
@@ -34030,10 +34432,10 @@
         <v>91</v>
       </c>
       <c r="V901" t="s">
-        <v>1916</v>
+        <v>2050</v>
       </c>
       <c r="W901" t="s">
-        <v>1607</v>
+        <v>1725</v>
       </c>
       <c r="X901" t="s">
         <v>1067</v>
@@ -34044,10 +34446,10 @@
         <v>91</v>
       </c>
       <c r="V902" t="s">
-        <v>1917</v>
+        <v>2051</v>
       </c>
       <c r="W902" t="s">
-        <v>1609</v>
+        <v>1729</v>
       </c>
       <c r="X902" t="s">
         <v>1067</v>
@@ -34058,10 +34460,10 @@
         <v>91</v>
       </c>
       <c r="V903" t="s">
-        <v>1918</v>
+        <v>2052</v>
       </c>
       <c r="W903" t="s">
-        <v>1609</v>
+        <v>1729</v>
       </c>
       <c r="X903" t="s">
         <v>1067</v>
@@ -34072,10 +34474,10 @@
         <v>91</v>
       </c>
       <c r="V904" t="s">
-        <v>1919</v>
+        <v>2053</v>
       </c>
       <c r="W904" t="s">
-        <v>1613</v>
+        <v>1737</v>
       </c>
       <c r="X904" t="s">
         <v>1067</v>
@@ -34086,10 +34488,10 @@
         <v>91</v>
       </c>
       <c r="V905" t="s">
-        <v>1920</v>
+        <v>2054</v>
       </c>
       <c r="W905" t="s">
-        <v>1613</v>
+        <v>1737</v>
       </c>
       <c r="X905" t="s">
         <v>1067</v>
@@ -34100,10 +34502,10 @@
         <v>91</v>
       </c>
       <c r="V906" t="s">
-        <v>1921</v>
+        <v>2055</v>
       </c>
       <c r="W906" t="s">
-        <v>1615</v>
+        <v>1741</v>
       </c>
       <c r="X906" t="s">
         <v>1067</v>
@@ -34114,10 +34516,10 @@
         <v>91</v>
       </c>
       <c r="V907" t="s">
-        <v>1922</v>
+        <v>2056</v>
       </c>
       <c r="W907" t="s">
-        <v>1615</v>
+        <v>1741</v>
       </c>
       <c r="X907" t="s">
         <v>1067</v>
@@ -34128,10 +34530,10 @@
         <v>91</v>
       </c>
       <c r="V908" t="s">
-        <v>1923</v>
+        <v>2057</v>
       </c>
       <c r="W908" t="s">
-        <v>1617</v>
+        <v>1745</v>
       </c>
       <c r="X908" t="s">
         <v>1067</v>
@@ -34142,10 +34544,10 @@
         <v>91</v>
       </c>
       <c r="V909" t="s">
-        <v>1924</v>
+        <v>2058</v>
       </c>
       <c r="W909" t="s">
-        <v>1617</v>
+        <v>1745</v>
       </c>
       <c r="X909" t="s">
         <v>1067</v>
@@ -34156,10 +34558,10 @@
         <v>91</v>
       </c>
       <c r="V910" t="s">
-        <v>1925</v>
+        <v>2059</v>
       </c>
       <c r="W910" t="s">
-        <v>1619</v>
+        <v>1749</v>
       </c>
       <c r="X910" t="s">
         <v>1067</v>
@@ -34170,10 +34572,10 @@
         <v>91</v>
       </c>
       <c r="V911" t="s">
-        <v>1926</v>
+        <v>2060</v>
       </c>
       <c r="W911" t="s">
-        <v>1619</v>
+        <v>1749</v>
       </c>
       <c r="X911" t="s">
         <v>1067</v>
@@ -34184,7 +34586,7 @@
         <v>91</v>
       </c>
       <c r="V912" t="s">
-        <v>1927</v>
+        <v>2061</v>
       </c>
       <c r="W912" t="s">
         <v>1010</v>
@@ -34198,7 +34600,7 @@
         <v>91</v>
       </c>
       <c r="V913" t="s">
-        <v>1928</v>
+        <v>2062</v>
       </c>
       <c r="W913" t="s">
         <v>1010</v>
@@ -34212,10 +34614,10 @@
         <v>91</v>
       </c>
       <c r="V914" t="s">
-        <v>1929</v>
+        <v>2063</v>
       </c>
       <c r="W914" t="s">
-        <v>1930</v>
+        <v>2064</v>
       </c>
       <c r="X914" t="s">
         <v>1067</v>
@@ -34226,10 +34628,10 @@
         <v>91</v>
       </c>
       <c r="V915" t="s">
-        <v>1931</v>
+        <v>2065</v>
       </c>
       <c r="W915" t="s">
-        <v>1930</v>
+        <v>2064</v>
       </c>
       <c r="X915" t="s">
         <v>1067</v>

--- a/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A89DDD7-8F2A-41BC-848C-745AC5831F46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B76CA744-88F0-4079-BC41-2B7081827892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6828,7 +6828,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C51C672-03AE-4463-8578-94F4EF7EA31C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDC91746-F087-4B08-91DE-239C64AC5E11}">
   <dimension ref="B2:AE915"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B76CA744-88F0-4079-BC41-2B7081827892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1299706F-F162-46DA-85EB-BF899A8E0799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6828,7 +6828,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDC91746-F087-4B08-91DE-239C64AC5E11}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93D82EC0-51F5-463F-BE7C-CB9C6C2BBEEA}">
   <dimension ref="B2:AE915"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1299706F-F162-46DA-85EB-BF899A8E0799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F138FC29-C181-4BE1-BADF-C83566742013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6828,7 +6828,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93D82EC0-51F5-463F-BE7C-CB9C6C2BBEEA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5736ED8-F5A6-4431-8EA9-783AF41262FC}">
   <dimension ref="B2:AE915"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F138FC29-C181-4BE1-BADF-C83566742013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8237F260-481D-4F79-BE75-E7D53B673F02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6828,7 +6828,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5736ED8-F5A6-4431-8EA9-783AF41262FC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03A37A9C-DCE1-4218-B093-82AB07A3DA0A}">
   <dimension ref="B2:AE915"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{18310C10-BEC1-40AE-BF1D-0DC6B66A21F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3FE88D04-2F1E-4E40-AE47-A42538B477C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7380,7 +7380,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ED2042A-808B-48D2-BC21-11DFCC3BA415}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CFC9F58-2F2E-4E54-A508-4F8D79D5CCCA}">
   <dimension ref="B2:AE1072"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3FE88D04-2F1E-4E40-AE47-A42538B477C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7D49BFB1-64D1-4408-B631-3E4BF0B4082C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7380,7 +7380,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CFC9F58-2F2E-4E54-A508-4F8D79D5CCCA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{904FC8DB-1C6E-4057-9BF6-29E6A9B2446F}">
   <dimension ref="B2:AE1072"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7D49BFB1-64D1-4408-B631-3E4BF0B4082C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5E9AB00-3D1A-40A5-A0D6-33B73AD92EA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7380,7 +7380,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{904FC8DB-1C6E-4057-9BF6-29E6A9B2446F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07C98DA1-87AF-4903-88AB-7CEDB84F31EB}">
   <dimension ref="B2:AE1072"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5E9AB00-3D1A-40A5-A0D6-33B73AD92EA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB45DCCC-7A53-44FD-9340-339002AD2AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7380,7 +7380,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07C98DA1-87AF-4903-88AB-7CEDB84F31EB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB5641A9-C8C0-4CF8-A5E4-E80839058367}">
   <dimension ref="B2:AE1072"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB45DCCC-7A53-44FD-9340-339002AD2AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2AE2A7B7-A7F6-49AD-8953-E4D916CBAE24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7380,7 +7380,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB5641A9-C8C0-4CF8-A5E4-E80839058367}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BD2DCFF-F349-4298-A797-C5EAF4C7B7FA}">
   <dimension ref="B2:AE1072"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2AE2A7B7-A7F6-49AD-8953-E4D916CBAE24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C655462-72E2-47C0-96CC-2A8B35AB1360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7380,7 +7380,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BD2DCFF-F349-4298-A797-C5EAF4C7B7FA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16EF090-DBCF-492F-BD3F-7CF0AD6CC19C}">
   <dimension ref="B2:AE1072"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C655462-72E2-47C0-96CC-2A8B35AB1360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F786F6F-BE22-4F0C-90A8-51C01EB979B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7380,7 +7380,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16EF090-DBCF-492F-BD3F-7CF0AD6CC19C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{988C0F0B-A8B8-4C89-813E-C46BD8AC489F}">
   <dimension ref="B2:AE1072"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F786F6F-BE22-4F0C-90A8-51C01EB979B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2655CD14-1A6C-4B32-B068-544A8246E2A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7380,7 +7380,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{988C0F0B-A8B8-4C89-813E-C46BD8AC489F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F3011D5-DB93-4729-A639-CE228A81D0AA}">
   <dimension ref="B2:AE1072"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2655CD14-1A6C-4B32-B068-544A8246E2A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8E802E2-D34D-43E4-BE2A-9B44A0433A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7380,7 +7380,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F3011D5-DB93-4729-A639-CE228A81D0AA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DA4C410-50EA-4BC7-B670-8767800D9136}">
   <dimension ref="B2:AE1072"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8E802E2-D34D-43E4-BE2A-9B44A0433A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8EAB86B-A2BF-4206-9393-3A40426F52B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7380,7 +7380,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DA4C410-50EA-4BC7-B670-8767800D9136}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C5C3A6E-D760-4A16-A548-2F8DBA06B6B8}">
   <dimension ref="B2:AE1072"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8EAB86B-A2BF-4206-9393-3A40426F52B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{651A25BA-9CE9-4379-B9B0-C9C8A0A5201E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7380,7 +7380,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C5C3A6E-D760-4A16-A548-2F8DBA06B6B8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67B455FA-F6A1-4D04-8E0A-5F4AAAA7C4E3}">
   <dimension ref="B2:AE1072"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{651A25BA-9CE9-4379-B9B0-C9C8A0A5201E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{77677D5A-DCE9-41A4-870F-8CA0F0741094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7380,7 +7380,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67B455FA-F6A1-4D04-8E0A-5F4AAAA7C4E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE9B167D-A7C0-48FC-8B3E-B6B1BE129CFE}">
   <dimension ref="B2:AE1072"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{77677D5A-DCE9-41A4-870F-8CA0F0741094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A4148E9B-8F75-4BF5-9F75-26594E8D25CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7380,7 +7380,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE9B167D-A7C0-48FC-8B3E-B6B1BE129CFE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06C8A186-2243-44B9-AA73-31593EDC1D2C}">
   <dimension ref="B2:AE1072"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A4148E9B-8F75-4BF5-9F75-26594E8D25CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{473B9742-9715-4B53-9072-417D9F9BCDF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7380,7 +7380,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06C8A186-2243-44B9-AA73-31593EDC1D2C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92CD291D-B979-4463-85EF-ABE673E6BB01}">
   <dimension ref="B2:AE1072"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{473B9742-9715-4B53-9072-417D9F9BCDF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0AE50020-FC51-4CC6-9380-ACDF0F9A13D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7380,7 +7380,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92CD291D-B979-4463-85EF-ABE673E6BB01}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB189729-AF25-4600-87D8-3A877E6134DE}">
   <dimension ref="B2:AE1072"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0AE50020-FC51-4CC6-9380-ACDF0F9A13D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{698DAE91-DC51-483C-85F9-F42B2346F969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7380,7 +7380,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB189729-AF25-4600-87D8-3A877E6134DE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BB6EC06-BE43-420E-8ED5-664118243D2E}">
   <dimension ref="B2:AE1072"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{698DAE91-DC51-483C-85F9-F42B2346F969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63522B3E-35D2-43CC-8FCC-018D58A4B9A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -124,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8840" uniqueCount="2257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8844" uniqueCount="2259">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -6894,7 +6894,13 @@
     <t>pset_set</t>
   </si>
   <si>
-    <t>ELE,DMD,PRE</t>
+    <t>STGOUT_BND</t>
+  </si>
+  <si>
+    <t>DMD,PRE,ELE</t>
+  </si>
+  <si>
+    <t>STG</t>
   </si>
 </sst>
 </file>
@@ -7381,10 +7387,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BB6EC06-BE43-420E-8ED5-664118243D2E}">
-  <dimension ref="B2:AE1072"/>
+  <dimension ref="B2:AF1072"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="2" spans="2:31" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -7398,7 +7404,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="3" spans="2:31" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -7451,7 +7457,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="4" spans="2:31" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>95</v>
       </c>
@@ -7513,10 +7519,13 @@
         <v>2254</v>
       </c>
       <c r="AE4" t="s">
+        <v>2256</v>
+      </c>
+      <c r="AF4" t="s">
         <v>2255</v>
       </c>
     </row>
-    <row r="5" spans="2:31" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>96</v>
       </c>
@@ -7577,11 +7586,11 @@
       <c r="AD5">
         <v>0</v>
       </c>
-      <c r="AE5" t="s">
-        <v>2256</v>
-      </c>
-    </row>
-    <row r="6" spans="2:31" x14ac:dyDescent="0.45">
+      <c r="AF5" t="s">
+        <v>2257</v>
+      </c>
+    </row>
+    <row r="6" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>97</v>
       </c>
@@ -7630,8 +7639,23 @@
       <c r="X6" t="s">
         <v>1067</v>
       </c>
-    </row>
-    <row r="7" spans="2:31" x14ac:dyDescent="0.45">
+      <c r="AA6" t="s">
+        <v>2250</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>2252</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>2</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>2258</v>
+      </c>
+    </row>
+    <row r="7" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>98</v>
       </c>
@@ -7681,7 +7705,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="8" spans="2:31" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>99</v>
       </c>
@@ -7731,7 +7755,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="9" spans="2:31" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>100</v>
       </c>
@@ -7781,7 +7805,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="10" spans="2:31" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>101</v>
       </c>
@@ -7831,7 +7855,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="11" spans="2:31" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>102</v>
       </c>
@@ -7881,7 +7905,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="12" spans="2:31" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>103</v>
       </c>
@@ -7931,7 +7955,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="13" spans="2:31" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>104</v>
       </c>
@@ -7981,7 +8005,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="14" spans="2:31" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>105</v>
       </c>
@@ -8031,7 +8055,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="15" spans="2:31" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>106</v>
       </c>
@@ -8081,7 +8105,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="16" spans="2:31" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>107</v>
       </c>
